--- a/markets/invest_map/dist/20261026_AI投資地圖_資料_v0.6.xlsx
+++ b/markets/invest_map/dist/20261026_AI投資地圖_資料_v0.6.xlsx
@@ -5740,7 +5740,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>nvidia/dist/20261025_NVIDIA模型_v0.2.xlsx Val!B57</t>
+          <t>nvidia/dist/20261025_NVIDIA模型_v0.2.1.xlsx Val!B57</t>
         </is>
       </c>
       <c r="H2">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>avgo/dist/20261025_Broadcom模型_v0.2.xlsx Val!B57</t>
+          <t>avgo/dist/20261025_Broadcom模型_v0.2.1.xlsx Val!B57</t>
         </is>
       </c>
       <c r="H3">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>skhynix/dist/20261025_SK海力士模型_v0.5.xlsx In!E6</t>
+          <t>skhynix/dist/20261025_SK海力士模型_v0.5.1.xlsx In!E6</t>
         </is>
       </c>
       <c r="H4">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>samsung/dist/20261025_三星電子模型_v0.3.xlsx In!E6</t>
+          <t>samsung/dist/20261025_三星電子模型_v0.3.1.xlsx In!E6</t>
         </is>
       </c>
       <c r="H5">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>micron/dist/20261025_美光模型_v0.4.xlsx In!E5</t>
+          <t>micron/dist/20261025_美光模型_v0.4.1.xlsx In!E5</t>
         </is>
       </c>
       <c r="H6">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>tsmc/dist/20261025_台積電模型_v0.3.xlsx In!E135</t>
+          <t>tsmc/dist/20261025_台積電模型_v0.3.1.xlsx In!E135</t>
         </is>
       </c>
       <c r="H7">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>arista/dist/20261025_Arista模型_v0.2.xlsx Val!B57</t>
+          <t>arista/dist/20261025_Arista模型_v0.2.1.xlsx Val!B57</t>
         </is>
       </c>
       <c r="H8">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>innolight/dist/20261025_中際旭創模型_v0.2.xlsx Val!B53</t>
+          <t>innolight/dist/20261026_中際旭創模型_v0.2.2.xlsx Val!B53</t>
         </is>
       </c>
       <c r="H9">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>delta/dist/20261025_台達電模型_v0.2.xlsx Val!B6</t>
+          <t>delta/dist/20261025_台達電模型_v0.2.1.xlsx Val!B6</t>
         </is>
       </c>
       <c r="H10">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>quanta/dist/20261025_廣達模型_v0.2.xlsx Val!B6</t>
+          <t>quanta/dist/20261025_廣達模型_v0.2.1.xlsx Val!B6</t>
         </is>
       </c>
       <c r="H11">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ibiden/dist/20261025_Ibiden模型_v0.2.xlsx Val!B6</t>
+          <t>ibiden/dist/20261025_Ibiden模型_v0.2.1.xlsx Val!B6</t>
         </is>
       </c>
       <c r="H12">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>advantest/dist/20261025_Advantest模型_v0.3.xlsx Val!B92</t>
+          <t>advantest/dist/20261025_Advantest模型_v0.3.1.xlsx Val!B92</t>
         </is>
       </c>
       <c r="H13">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>disco/dist/20261025_Disco模型_v0.2.1.xlsx Val!B53</t>
+          <t>disco/dist/20261025_Disco模型_v0.2.2.xlsx Val!B53</t>
         </is>
       </c>
       <c r="H14">
@@ -6108,16 +6108,16 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>529.76</v>
+        <v>532.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>microsoft/dist/20261025_Microsoft收支模型_v0_2_2.xlsx 輸入與假設!C345</t>
+          <t>microsoft/dist/20261027_Microsoft個股模型_v0.3.xlsx Val!B39</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="H15">
-        <f>IF(ISNUMBER(F15),F15,C15)</f>
+        <f>C15</f>
         <v/>
       </c>
     </row>
@@ -6145,16 +6145,16 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>259.92</v>
+        <v>249.09</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>amazon/dist/20261025_Amazon收支模型_v0_2_2.xlsx 輸入與假設!C328</t>
+          <t>amazon/dist/20261027_Amazon個股模型_v0.3.xlsx Val!B20</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
@@ -6166,7 +6166,7 @@
         </is>
       </c>
       <c r="H16">
-        <f>IF(ISNUMBER(F16),F16,C16)</f>
+        <f>C16</f>
         <v/>
       </c>
     </row>
@@ -6182,16 +6182,16 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>350.5</v>
+        <v>316.8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>alphabet/dist/20261025_Alphabet收支模型_v0_2_2.xlsx 輸入與假設!C374</t>
+          <t>alphabet/dist/20261027_Alphabet個股模型_v0.3.xlsx Val!B9</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="H17">
-        <f>IF(ISNUMBER(F17),F17,C17)</f>
+        <f>C17</f>
         <v/>
       </c>
     </row>
@@ -6219,16 +6219,16 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>129.13</v>
+        <v>126.06</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>oracle/dist/20261022_Oracle收支模型_v0_3_1.xlsx 輸入與假設!C175</t>
+          <t>oracle/dist/20261027_Oracle個股模型_v0.4.xlsx Val!C4</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
@@ -6240,7 +6240,7 @@
         </is>
       </c>
       <c r="H18">
-        <f>IF(ISNUMBER(F18),F18,C18)</f>
+        <f>C18</f>
         <v/>
       </c>
     </row>
@@ -6302,7 +6302,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>nebius/dist/20261022_Nebius收支模型_v0_5.xlsx 輸入與假設!C125</t>
+          <t>nebius/dist/20261022_Nebius收支模型_v0_5_1.xlsx 輸入與假設!C125</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>amd/dist/20261025_AMD模型_v0.2.1.xlsx Val!B67</t>
+          <t>amd/dist/20261025_AMD模型_v0.2.2.xlsx Val!B67</t>
         </is>
       </c>
       <c r="H26">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>mediatek/dist/20261025_聯發科模型_v0.1.xlsx Val!B53</t>
+          <t>mediatek/dist/20261025_聯發科模型_v0.1.1.xlsx Val!B53</t>
         </is>
       </c>
       <c r="H27">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>mrvl/dist/20261025_邁威爾模型_v0.2.xlsx Val!B68</t>
+          <t>mrvl/dist/20261026_邁威爾模型_v0.2.2.xlsx Val!B68</t>
         </is>
       </c>
       <c r="H28">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>alchip/dist/20261025_世芯-KY模型_v0.1.xlsx Val!B53</t>
+          <t>alchip/dist/20261025_世芯-KY模型_v0.1.1.xlsx Val!B53</t>
         </is>
       </c>
       <c r="H29">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>guc/dist/20261025_創意模型_v0.1.xlsx Val!B53</t>
+          <t>guc/dist/20261025_創意模型_v0.1.1.xlsx Val!B53</t>
         </is>
       </c>
       <c r="H30">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>cohr/dist/20261025_Coherent模型_v0.2.xlsx Val!B64</t>
+          <t>cohr/dist/20261026_Coherent模型_v0.2.2.xlsx Val!B64</t>
         </is>
       </c>
       <c r="H33">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>lite/dist/20261025_Lumentum模型_v0.2.xlsx Val!B63</t>
+          <t>lite/dist/20261026_Lumentum模型_v0.2.2.xlsx Val!B63</t>
         </is>
       </c>
       <c r="H34">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>eoptolink/dist/20261025_新易盛模型_v0.2.xlsx Val!B63</t>
+          <t>eoptolink/dist/20261026_新易盛模型_v0.2.2.xlsx Val!B63</t>
         </is>
       </c>
       <c r="H35">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>accton/dist/20261025_智邦模型_v0.2.xlsx Val!B66</t>
+          <t>accton/dist/20261025_智邦模型_v0.2.1.xlsx Val!B66</t>
         </is>
       </c>
       <c r="H36">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>fabrinet/dist/20261025_Fabrinet模型_v0.1.xlsx Val!B64</t>
+          <t>fabrinet/dist/20261026_Fabrinet模型_v0.1.2.xlsx Val!B64</t>
         </is>
       </c>
       <c r="H37">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>crdo/dist/20261025_Credo模型_v0.2.xlsx Val!B63</t>
+          <t>crdo/dist/20261026_Credo模型_v0.2.2.xlsx Val!B63</t>
         </is>
       </c>
       <c r="H38">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>alab/dist/20261025_Astera Labs模型_v0.1.xlsx Val!B63</t>
+          <t>alab/dist/20261025_Astera Labs模型_v0.1.1.xlsx Val!B63</t>
         </is>
       </c>
       <c r="H39">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>kyec/dist/20261025_京元電模型_v0.2.xlsx Val!B53</t>
+          <t>kyec/dist/20261025_京元電模型_v0.2.1.xlsx Val!B53</t>
         </is>
       </c>
       <c r="H40">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>amkr/dist/20261025_艾克爾模型_v0.2.xlsx Val!B53</t>
+          <t>amkr/dist/20261025_艾克爾模型_v0.2.1.xlsx Val!B53</t>
         </is>
       </c>
       <c r="H41">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>emc/dist/20261025_台光電模型_v0.2.xlsx Val!B6</t>
+          <t>emc/dist/20261025_台光電模型_v0.2.1.xlsx Val!B6</t>
         </is>
       </c>
       <c r="H42">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>unimicron/dist/20261025_欣興模型_v0.1.xlsx Val!B53</t>
+          <t>unimicron/dist/20261025_欣興模型_v0.1.1.xlsx Val!B53</t>
         </is>
       </c>
       <c r="H43">
@@ -6999,7 +6999,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>nanya_pcb/dist/20261025_南電模型_v0.1.xlsx Val!B53</t>
+          <t>nanya_pcb/dist/20261025_南電模型_v0.1.1.xlsx Val!B53</t>
         </is>
       </c>
       <c r="H44">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>gce/dist/20261025_金像電模型_v0.1.xlsx Val!B53</t>
+          <t>gce/dist/20261025_金像電模型_v0.1.1.xlsx Val!B53</t>
         </is>
       </c>
       <c r="H45">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>victory_giant/dist/20261025_勝宏科技模型_v0.1.xlsx Val!B53</t>
+          <t>victory_giant/dist/20261025_勝宏科技模型_v0.1.1.xlsx Val!B53</t>
         </is>
       </c>
       <c r="H46">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>asml/dist/20261025_ASML模型_v0.2.xlsx Val!B16</t>
+          <t>asml/dist/20261025_ASML模型_v0.2.1.xlsx Val!B16</t>
         </is>
       </c>
       <c r="H47">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>amat/dist/20261025_應用材料模型_v0.2.xlsx In!E139</t>
+          <t>amat/dist/20261025_應用材料模型_v0.2.1.xlsx In!E139</t>
         </is>
       </c>
       <c r="H48">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>lrcx/dist/20261025_科林研發模型_v0.2.xlsx In!E124</t>
+          <t>lrcx/dist/20261025_科林研發模型_v0.2.1.xlsx In!E124</t>
         </is>
       </c>
       <c r="H49">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>klac/dist/20261025_科磊模型_v0.2.xlsx In!E55</t>
+          <t>klac/dist/20261025_科磊模型_v0.2.1.xlsx In!E55</t>
         </is>
       </c>
       <c r="H50">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>hanmi/dist/20261025_韓美半導體模型_v0.2.1.xlsx In!E95</t>
+          <t>hanmi/dist/20261025_韓美半導體模型_v0.2.2.xlsx In!E95</t>
         </is>
       </c>
       <c r="H51">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ter/dist/20261025_泰瑞達模型_v0.1.xlsx Val!B73</t>
+          <t>ter/dist/20261025_泰瑞達模型_v0.1.1.xlsx Val!B73</t>
         </is>
       </c>
       <c r="H52">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>besi/dist/20261025_BESI模型_v0.1.xlsx In!E117</t>
+          <t>besi/dist/20261025_BESI模型_v0.1.1.xlsx In!E117</t>
         </is>
       </c>
       <c r="H53">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>towa/dist/20261025_TOWA模型_v0.1.xlsx Val!B110</t>
+          <t>towa/dist/20261025_TOWA模型_v0.1.1.xlsx Val!B110</t>
         </is>
       </c>
       <c r="H54">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>accretech/dist/20261025_東京精密模型_v0.1.xlsx Val!B53</t>
+          <t>accretech/dist/20261025_東京精密模型_v0.1.1.xlsx Val!B53</t>
         </is>
       </c>
       <c r="H55">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>foxconn/dist/20261025_鴻海模型_v0.2.xlsx Val!B6</t>
+          <t>foxconn/dist/20261025_鴻海模型_v0.2.1.xlsx Val!B6</t>
         </is>
       </c>
       <c r="H56">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>wistron/dist/20261025_緯創模型_v0.1.xlsx Val!B53</t>
+          <t>wistron/dist/20261025_緯創模型_v0.1.1.xlsx Val!B53</t>
         </is>
       </c>
       <c r="H57">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>wiwynn/dist/20261025_緯穎模型_v0.1.xlsx Val!B53</t>
+          <t>wiwynn/dist/20261025_緯穎模型_v0.1.1.xlsx Val!B53</t>
         </is>
       </c>
       <c r="H58">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>smci/dist/20261025_美超微模型_v0.1.xlsx Val!B53</t>
+          <t>smci/dist/20261025_美超微模型_v0.1.1.xlsx Val!B53</t>
         </is>
       </c>
       <c r="H60">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>avc/dist/20261025_奇鋐模型_v0.2.xlsx Val!B6</t>
+          <t>avc/dist/20261025_奇鋐模型_v0.2.1.xlsx Val!B6</t>
         </is>
       </c>
       <c r="H61">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>liteon/dist/20261025_光寶模型_v0.1.xlsx Val!B53</t>
+          <t>liteon/dist/20261025_光寶模型_v0.1.1.xlsx Val!B53</t>
         </is>
       </c>
       <c r="H62">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>auras/dist/20261025_雙鴻模型_v0.1.xlsx Val!B62</t>
+          <t>auras/dist/20261025_雙鴻模型_v0.1.1.xlsx Val!B62</t>
         </is>
       </c>
       <c r="H63">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>jentech/dist/20261025_健策模型_v0.1.xlsx Val!B56</t>
+          <t>jentech/dist/20261025_健策模型_v0.1.1.xlsx Val!B56</t>
         </is>
       </c>
       <c r="H64">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>nvidia/dist/20261025_NVIDIA模型_v0.2.xlsx Val!B40</t>
+          <t>nvidia/dist/20261025_NVIDIA模型_v0.2.1.xlsx Val!B40</t>
         </is>
       </c>
       <c r="J2" s="4" t="n">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>nvidia/dist/20261025_NVIDIA模型_v0.2.xlsx Val!B47</t>
+          <t>nvidia/dist/20261025_NVIDIA模型_v0.2.1.xlsx Val!B47</t>
         </is>
       </c>
       <c r="N2">
@@ -7887,9 +7887,10 @@
         <f>P2/N2-1</f>
         <v/>
       </c>
-      <c r="S2">
-        <f>IF(Q2&gt;0.5,"強力買進",IF(Q2&gt;0.25,"買進",IF(Q2&gt;=-0.25,"中立",IF(Q2&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S2" s="4" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
       </c>
       <c r="T2">
         <f>467.571184194614/N2-1</f>
@@ -7941,7 +7942,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>[Derived] nvidia/dist/20261025_NVIDIA模型_v0.2.xlsx PL!D12…PL!G292</t>
+          <t>[Derived] nvidia/dist/20261025_NVIDIA模型_v0.2.1.xlsx PL!D12…PL!G292</t>
         </is>
       </c>
       <c r="AH2">
@@ -7952,13 +7953,14 @@
         <f>IF(S2="未上市","未上市",IF(AND(AH2="不通過",OR(S2="強力買進",S2="買進",S2="未估值")),"收支不足",S2))</f>
         <v/>
       </c>
-      <c r="AJ2">
-        <f>IF(Q2&gt;0.5,"大於 50%",IF(Q2&gt;0.25,"25%–50%",IF(Q2&gt;=0,"0%–25%",IF(Q2&gt;=-0.25,"0%～−25%",IF(Q2&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ2" s="4" t="inlineStr">
+        <is>
+          <t>0%–25%</t>
+        </is>
       </c>
       <c r="AK2" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 nvidia/dist/20261025_NVIDIA模型_v0.2.xlsx Val!B43；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 nvidia/dist/20261025_NVIDIA模型_v0.2.1.xlsx Val!B43；投資建議 nvidia/dist/20261025_NVIDIA模型_v0.2.1.xlsx Val!B179；級距 nvidia/dist/20261025_NVIDIA模型_v0.2.1.xlsx Val!B178</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7994,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>avgo/dist/20261025_Broadcom模型_v0.2.xlsx Val!B40</t>
+          <t>avgo/dist/20261025_Broadcom模型_v0.2.1.xlsx Val!B40</t>
         </is>
       </c>
       <c r="J3" s="4" t="n">
@@ -8000,7 +8002,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>avgo/dist/20261025_Broadcom模型_v0.2.xlsx Val!B47</t>
+          <t>avgo/dist/20261025_Broadcom模型_v0.2.1.xlsx Val!B47</t>
         </is>
       </c>
       <c r="N3">
@@ -8022,9 +8024,10 @@
         <f>P3/N3-1</f>
         <v/>
       </c>
-      <c r="S3">
-        <f>IF(Q3&gt;0.5,"強力買進",IF(Q3&gt;0.25,"買進",IF(Q3&gt;=-0.25,"中立",IF(Q3&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
       </c>
       <c r="T3">
         <f>647.367676593253/N3-1</f>
@@ -8076,7 +8079,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>[Derived] avgo/dist/20261025_Broadcom模型_v0.2.xlsx PL!D13…PL!G39</t>
+          <t>[Derived] avgo/dist/20261025_Broadcom模型_v0.2.1.xlsx PL!D13…PL!G39</t>
         </is>
       </c>
       <c r="AH3">
@@ -8087,13 +8090,14 @@
         <f>IF(S3="未上市","未上市",IF(AND(AH3="不通過",OR(S3="強力買進",S3="買進",S3="未估值")),"收支不足",S3))</f>
         <v/>
       </c>
-      <c r="AJ3">
-        <f>IF(Q3&gt;0.5,"大於 50%",IF(Q3&gt;0.25,"25%–50%",IF(Q3&gt;=0,"0%–25%",IF(Q3&gt;=-0.25,"0%～−25%",IF(Q3&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ3" s="4" t="inlineStr">
+        <is>
+          <t>0%–25%</t>
+        </is>
       </c>
       <c r="AK3" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 avgo/dist/20261025_Broadcom模型_v0.2.xlsx Val!B43；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 avgo/dist/20261025_Broadcom模型_v0.2.1.xlsx Val!B43；投資建議 avgo/dist/20261025_Broadcom模型_v0.2.1.xlsx Val!B113；級距 avgo/dist/20261025_Broadcom模型_v0.2.1.xlsx Val!B112</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8131,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>skhynix/dist/20261025_SK海力士模型_v0.5.xlsx Val!B161</t>
+          <t>skhynix/dist/20261025_SK海力士模型_v0.5.1.xlsx Val!B161</t>
         </is>
       </c>
       <c r="J4" s="4" t="n">
@@ -8135,7 +8139,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>skhynix/dist/20261025_SK海力士模型_v0.5.xlsx Val!D145</t>
+          <t>skhynix/dist/20261025_SK海力士模型_v0.5.1.xlsx Val!D145</t>
         </is>
       </c>
       <c r="N4">
@@ -8157,9 +8161,10 @@
         <f>P4/N4-1</f>
         <v/>
       </c>
-      <c r="S4">
-        <f>IF(Q4&gt;0.5,"強力買進",IF(Q4&gt;0.25,"買進",IF(Q4&gt;=-0.25,"中立",IF(Q4&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>強力買進</t>
+        </is>
       </c>
       <c r="T4">
         <f>1392208.55280262/N4-1</f>
@@ -8206,7 +8211,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>[Derived] skhynix/dist/20261025_SK海力士模型_v0.5.xlsx Y!C22…Y!L22</t>
+          <t>[Derived] skhynix/dist/20261025_SK海力士模型_v0.5.1.xlsx Y!C22…Y!L22</t>
         </is>
       </c>
       <c r="AH4">
@@ -8217,13 +8222,14 @@
         <f>IF(S4="未上市","未上市",IF(AND(AH4="不通過",OR(S4="強力買進",S4="買進",S4="未估值")),"收支不足",S4))</f>
         <v/>
       </c>
-      <c r="AJ4">
-        <f>IF(Q4&gt;0.5,"大於 50%",IF(Q4&gt;0.25,"25%–50%",IF(Q4&gt;=0,"0%–25%",IF(Q4&gt;=-0.25,"0%～−25%",IF(Q4&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ4" s="4" t="inlineStr">
+        <is>
+          <t>大於 50%</t>
+        </is>
       </c>
       <c r="AK4" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 skhynix/dist/20261025_SK海力士模型_v0.5.xlsx Val!B164；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 skhynix/dist/20261025_SK海力士模型_v0.5.1.xlsx Val!B164；投資建議 skhynix/dist/20261025_SK海力士模型_v0.5.1.xlsx Val!B185；級距 skhynix/dist/20261025_SK海力士模型_v0.5.1.xlsx Val!B184</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8263,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>samsung/dist/20261025_三星電子模型_v0.3.xlsx Val!B161</t>
+          <t>samsung/dist/20261025_三星電子模型_v0.3.1.xlsx Val!B161</t>
         </is>
       </c>
       <c r="J5" s="4" t="n">
@@ -8265,7 +8271,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>samsung/dist/20261025_三星電子模型_v0.3.xlsx Val!D145</t>
+          <t>samsung/dist/20261025_三星電子模型_v0.3.1.xlsx Val!D145</t>
         </is>
       </c>
       <c r="N5">
@@ -8287,9 +8293,10 @@
         <f>P5/N5-1</f>
         <v/>
       </c>
-      <c r="S5">
-        <f>IF(Q5&gt;0.5,"強力買進",IF(Q5&gt;0.25,"買進",IF(Q5&gt;=-0.25,"中立",IF(Q5&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>強力買進</t>
+        </is>
       </c>
       <c r="T5">
         <f>255831.994790815/N5-1</f>
@@ -8336,7 +8343,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>[Derived] samsung/dist/20261025_三星電子模型_v0.3.xlsx Y!C22…Y!L22</t>
+          <t>[Derived] samsung/dist/20261025_三星電子模型_v0.3.1.xlsx Y!C22…Y!L22</t>
         </is>
       </c>
       <c r="AH5">
@@ -8347,13 +8354,14 @@
         <f>IF(S5="未上市","未上市",IF(AND(AH5="不通過",OR(S5="強力買進",S5="買進",S5="未估值")),"收支不足",S5))</f>
         <v/>
       </c>
-      <c r="AJ5">
-        <f>IF(Q5&gt;0.5,"大於 50%",IF(Q5&gt;0.25,"25%–50%",IF(Q5&gt;=0,"0%–25%",IF(Q5&gt;=-0.25,"0%～−25%",IF(Q5&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ5" s="4" t="inlineStr">
+        <is>
+          <t>大於 50%</t>
+        </is>
       </c>
       <c r="AK5" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 samsung/dist/20261025_三星電子模型_v0.3.xlsx Val!B164；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 samsung/dist/20261025_三星電子模型_v0.3.1.xlsx Val!B164；投資建議 samsung/dist/20261025_三星電子模型_v0.3.1.xlsx Val!B185；級距 samsung/dist/20261025_三星電子模型_v0.3.1.xlsx Val!B184</t>
         </is>
       </c>
     </row>
@@ -8387,7 +8395,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>micron/dist/20261025_美光模型_v0.4.xlsx Val!B208</t>
+          <t>micron/dist/20261025_美光模型_v0.4.1.xlsx Val!B208</t>
         </is>
       </c>
       <c r="J6" s="4" t="n">
@@ -8395,7 +8403,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>micron/dist/20261025_美光模型_v0.4.xlsx Val!D192</t>
+          <t>micron/dist/20261025_美光模型_v0.4.1.xlsx Val!D192</t>
         </is>
       </c>
       <c r="N6">
@@ -8417,9 +8425,10 @@
         <f>P6/N6-1</f>
         <v/>
       </c>
-      <c r="S6">
-        <f>IF(Q6&gt;0.5,"強力買進",IF(Q6&gt;0.25,"買進",IF(Q6&gt;=-0.25,"中立",IF(Q6&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
       </c>
       <c r="T6">
         <f>348.754265504643/N6-1</f>
@@ -8466,7 +8475,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>[Derived] micron/dist/20261025_美光模型_v0.4.xlsx Y!C22…Y!L22</t>
+          <t>[Derived] micron/dist/20261025_美光模型_v0.4.1.xlsx Y!C22…Y!L22</t>
         </is>
       </c>
       <c r="AH6">
@@ -8477,13 +8486,14 @@
         <f>IF(S6="未上市","未上市",IF(AND(AH6="不通過",OR(S6="強力買進",S6="買進",S6="未估值")),"收支不足",S6))</f>
         <v/>
       </c>
-      <c r="AJ6">
-        <f>IF(Q6&gt;0.5,"大於 50%",IF(Q6&gt;0.25,"25%–50%",IF(Q6&gt;=0,"0%–25%",IF(Q6&gt;=-0.25,"0%～−25%",IF(Q6&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ6" s="4" t="inlineStr">
+        <is>
+          <t>0%～−25%</t>
+        </is>
       </c>
       <c r="AK6" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 micron/dist/20261025_美光模型_v0.4.xlsx Val!B211；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 micron/dist/20261025_美光模型_v0.4.1.xlsx Val!B211；投資建議 micron/dist/20261025_美光模型_v0.4.1.xlsx Val!B232；級距 micron/dist/20261025_美光模型_v0.4.1.xlsx Val!B231</t>
         </is>
       </c>
     </row>
@@ -8517,7 +8527,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tsmc/dist/20261025_台積電模型_v0.3.xlsx Val!B94</t>
+          <t>tsmc/dist/20261025_台積電模型_v0.3.1.xlsx Val!B94</t>
         </is>
       </c>
       <c r="J7" s="4" t="n">
@@ -8525,7 +8535,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>tsmc/dist/20261025_台積電模型_v0.3.xlsx Val!D78</t>
+          <t>tsmc/dist/20261025_台積電模型_v0.3.1.xlsx Val!D78</t>
         </is>
       </c>
       <c r="N7">
@@ -8547,9 +8557,10 @@
         <f>P7/N7-1</f>
         <v/>
       </c>
-      <c r="S7">
-        <f>IF(Q7&gt;0.5,"強力買進",IF(Q7&gt;0.25,"買進",IF(Q7&gt;=-0.25,"中立",IF(Q7&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
       </c>
       <c r="T7">
         <f>3022.97680876707/N7-1</f>
@@ -8596,7 +8607,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>[Derived] tsmc/dist/20261025_台積電模型_v0.3.xlsx PL!B12…PL!T12</t>
+          <t>[Derived] tsmc/dist/20261025_台積電模型_v0.3.1.xlsx PL!B12…PL!T12</t>
         </is>
       </c>
       <c r="AH7">
@@ -8607,13 +8618,14 @@
         <f>IF(S7="未上市","未上市",IF(AND(AH7="不通過",OR(S7="強力買進",S7="買進",S7="未估值")),"收支不足",S7))</f>
         <v/>
       </c>
-      <c r="AJ7">
-        <f>IF(Q7&gt;0.5,"大於 50%",IF(Q7&gt;0.25,"25%–50%",IF(Q7&gt;=0,"0%–25%",IF(Q7&gt;=-0.25,"0%～−25%",IF(Q7&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ7" s="4" t="inlineStr">
+        <is>
+          <t>0%–25%</t>
+        </is>
       </c>
       <c r="AK7" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 tsmc/dist/20261025_台積電模型_v0.3.xlsx Val!B97；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 tsmc/dist/20261025_台積電模型_v0.3.1.xlsx Val!B97；投資建議 tsmc/dist/20261025_台積電模型_v0.3.1.xlsx Val!B116；級距 tsmc/dist/20261025_台積電模型_v0.3.1.xlsx Val!B115</t>
         </is>
       </c>
     </row>
@@ -8647,7 +8659,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>arista/dist/20261025_Arista模型_v0.2.xlsx Val!B40</t>
+          <t>arista/dist/20261025_Arista模型_v0.2.1.xlsx Val!B40</t>
         </is>
       </c>
       <c r="J8" s="4" t="n">
@@ -8655,7 +8667,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>arista/dist/20261025_Arista模型_v0.2.xlsx Val!B47</t>
+          <t>arista/dist/20261025_Arista模型_v0.2.1.xlsx Val!B47</t>
         </is>
       </c>
       <c r="N8">
@@ -8677,9 +8689,10 @@
         <f>P8/N8-1</f>
         <v/>
       </c>
-      <c r="S8">
-        <f>IF(Q8&gt;0.5,"強力買進",IF(Q8&gt;0.25,"買進",IF(Q8&gt;=-0.25,"中立",IF(Q8&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>放空</t>
+        </is>
       </c>
       <c r="T8">
         <f>174.075889279442/N8-1</f>
@@ -8731,7 +8744,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>[Derived] arista/dist/20261025_Arista模型_v0.2.xlsx PL!D12…PL!G36</t>
+          <t>[Derived] arista/dist/20261025_Arista模型_v0.2.1.xlsx PL!D12…PL!G36</t>
         </is>
       </c>
       <c r="AH8">
@@ -8742,13 +8755,14 @@
         <f>IF(S8="未上市","未上市",IF(AND(AH8="不通過",OR(S8="強力買進",S8="買進",S8="未估值")),"收支不足",S8))</f>
         <v/>
       </c>
-      <c r="AJ8">
-        <f>IF(Q8&gt;0.5,"大於 50%",IF(Q8&gt;0.25,"25%–50%",IF(Q8&gt;=0,"0%–25%",IF(Q8&gt;=-0.25,"0%～−25%",IF(Q8&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ8" s="4" t="inlineStr">
+        <is>
+          <t>−25%～−50%</t>
+        </is>
       </c>
       <c r="AK8" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 arista/dist/20261025_Arista模型_v0.2.xlsx Val!B43；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 arista/dist/20261025_Arista模型_v0.2.1.xlsx Val!B43；投資建議 arista/dist/20261025_Arista模型_v0.2.1.xlsx Val!B53；級距 arista/dist/20261025_Arista模型_v0.2.1.xlsx Val!B52</t>
         </is>
       </c>
     </row>
@@ -8778,19 +8792,19 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1355.25565207254</v>
+        <v>1343.19997585911</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>innolight/dist/20261025_中際旭創模型_v0.2.xlsx Val!B39</t>
+          <t>innolight/dist/20261026_中際旭創模型_v0.2.2.xlsx Val!B39</t>
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>498.176089619339</v>
+        <v>503.748980706021</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>innolight/dist/20261025_中際旭創模型_v0.2.xlsx Val!D23</t>
+          <t>innolight/dist/20261026_中際旭創模型_v0.2.2.xlsx Val!D23</t>
         </is>
       </c>
       <c r="N9">
@@ -8806,18 +8820,19 @@
         <v/>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>1.21219276247089</v>
+        <v>1.19251420246985</v>
       </c>
       <c r="R9">
         <f>P9/N9-1</f>
         <v/>
       </c>
-      <c r="S9">
-        <f>IF(Q9&gt;0.5,"強力買進",IF(Q9&gt;0.25,"買進",IF(Q9&gt;=-0.25,"中立",IF(Q9&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>強力買進</t>
+        </is>
       </c>
       <c r="T9">
-        <f>2265.72535634618/N9-1</f>
+        <f>2256.55339542562/N9-1</f>
         <v/>
       </c>
       <c r="U9" t="inlineStr">
@@ -8827,12 +8842,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>12.3 ／ 15.5 ／ 21.0</t>
+          <t>12.7 ／ 15.5 ／ 20.7</t>
         </is>
       </c>
       <c r="W9" s="1" t="inlineStr">
         <is>
-          <t>DCF 目標價 831.5（Val!B24）；Comparable 目標價 1,879.1（Val!B40）；市場共識目標價 1,321.0（Val!B41，外部、僅供對照）；價格帶 C～A 情境 DCF 498.2～1,049.4</t>
+          <t>DCF 目標價 822.8（Val!B24）；Comparable 目標價 1,863.6（Val!B40）；市場共識目標價 1,321.0（Val!B41，外部、僅供對照）；價格帶 C～A 情境 DCF 503.7～1,016.9</t>
         </is>
       </c>
       <c r="Z9">
@@ -8855,18 +8870,18 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>17 個情境年度淨利（不含實績），全部為正</t>
+          <t>19 個情境年度淨利（不含實績），全部為正</t>
         </is>
       </c>
       <c r="AE9" s="4" t="n">
-        <v>1034.162783109114</v>
+        <v>1134.801727141911</v>
       </c>
       <c r="AF9" s="4" t="n">
         <v>31.8281188474012</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>[Derived] innolight/dist/20261025_中際旭創模型_v0.2.xlsx PL!D12…PL!J36</t>
+          <t>[Derived] innolight/dist/20261026_中際旭創模型_v0.2.2.xlsx PL!D12…PL!J36</t>
         </is>
       </c>
       <c r="AH9">
@@ -8877,13 +8892,14 @@
         <f>IF(S9="未上市","未上市",IF(AND(AH9="不通過",OR(S9="強力買進",S9="買進",S9="未估值")),"收支不足",S9))</f>
         <v/>
       </c>
-      <c r="AJ9">
-        <f>IF(Q9&gt;0.5,"大於 50%",IF(Q9&gt;0.25,"25%–50%",IF(Q9&gt;=0,"0%–25%",IF(Q9&gt;=-0.25,"0%～−25%",IF(Q9&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ9" s="4" t="inlineStr">
+        <is>
+          <t>大於 50%</t>
+        </is>
       </c>
       <c r="AK9" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 innolight/dist/20261025_中際旭創模型_v0.2.xlsx Val!B42；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 innolight/dist/20261026_中際旭創模型_v0.2.2.xlsx Val!B42；投資建議 innolight/dist/20261026_中際旭創模型_v0.2.2.xlsx Val!B50；級距 innolight/dist/20261026_中際旭創模型_v0.2.2.xlsx Val!B49</t>
         </is>
       </c>
     </row>
@@ -8917,7 +8933,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>delta/dist/20261025_台達電模型_v0.2.xlsx Val!B119</t>
+          <t>delta/dist/20261025_台達電模型_v0.2.1.xlsx Val!B119</t>
         </is>
       </c>
       <c r="J10" s="4" t="n">
@@ -8925,7 +8941,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>delta/dist/20261025_台達電模型_v0.2.xlsx Val!D104</t>
+          <t>delta/dist/20261025_台達電模型_v0.2.1.xlsx Val!D104</t>
         </is>
       </c>
       <c r="N10">
@@ -8947,9 +8963,10 @@
         <f>P10/N10-1</f>
         <v/>
       </c>
-      <c r="S10">
-        <f>IF(Q10&gt;0.5,"強力買進",IF(Q10&gt;0.25,"買進",IF(Q10&gt;=-0.25,"中立",IF(Q10&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
       </c>
       <c r="T10">
         <f>1360.0134167175/N10-1</f>
@@ -9001,7 +9018,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>[Derived] delta/dist/20261025_台達電模型_v0.2.xlsx PL!D13…PL!G39</t>
+          <t>[Derived] delta/dist/20261025_台達電模型_v0.2.1.xlsx PL!D13…PL!G39</t>
         </is>
       </c>
       <c r="AH10">
@@ -9012,13 +9029,14 @@
         <f>IF(S10="未上市","未上市",IF(AND(AH10="不通過",OR(S10="強力買進",S10="買進",S10="未估值")),"收支不足",S10))</f>
         <v/>
       </c>
-      <c r="AJ10">
-        <f>IF(Q10&gt;0.5,"大於 50%",IF(Q10&gt;0.25,"25%–50%",IF(Q10&gt;=0,"0%–25%",IF(Q10&gt;=-0.25,"0%～−25%",IF(Q10&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ10" s="4" t="inlineStr">
+        <is>
+          <t>0%～−25%</t>
+        </is>
       </c>
       <c r="AK10" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 delta/dist/20261025_台達電模型_v0.2.xlsx Val!B122；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 delta/dist/20261025_台達電模型_v0.2.1.xlsx Val!B122；投資建議 delta/dist/20261025_台達電模型_v0.2.1.xlsx Val!B135；級距 delta/dist/20261025_台達電模型_v0.2.1.xlsx Val!B134</t>
         </is>
       </c>
     </row>
@@ -9052,7 +9070,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>quanta/dist/20261025_廣達模型_v0.2.xlsx Val!B120</t>
+          <t>quanta/dist/20261025_廣達模型_v0.2.1.xlsx Val!B120</t>
         </is>
       </c>
       <c r="J11" s="4" t="n">
@@ -9060,7 +9078,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>quanta/dist/20261025_廣達模型_v0.2.xlsx Val!D104</t>
+          <t>quanta/dist/20261025_廣達模型_v0.2.1.xlsx Val!D104</t>
         </is>
       </c>
       <c r="N11">
@@ -9082,9 +9100,10 @@
         <f>P11/N11-1</f>
         <v/>
       </c>
-      <c r="S11">
-        <f>IF(Q11&gt;0.5,"強力買進",IF(Q11&gt;0.25,"買進",IF(Q11&gt;=-0.25,"中立",IF(Q11&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S11" s="4" t="inlineStr">
+        <is>
+          <t>強力買進</t>
+        </is>
       </c>
       <c r="T11">
         <f>490.548184039647/N11-1</f>
@@ -9136,7 +9155,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>[Derived] quanta/dist/20261025_廣達模型_v0.2.xlsx PL!D13…PL!G39</t>
+          <t>[Derived] quanta/dist/20261025_廣達模型_v0.2.1.xlsx PL!D13…PL!G39</t>
         </is>
       </c>
       <c r="AH11">
@@ -9147,13 +9166,14 @@
         <f>IF(S11="未上市","未上市",IF(AND(AH11="不通過",OR(S11="強力買進",S11="買進",S11="未估值")),"收支不足",S11))</f>
         <v/>
       </c>
-      <c r="AJ11">
-        <f>IF(Q11&gt;0.5,"大於 50%",IF(Q11&gt;0.25,"25%–50%",IF(Q11&gt;=0,"0%–25%",IF(Q11&gt;=-0.25,"0%～−25%",IF(Q11&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ11" s="4" t="inlineStr">
+        <is>
+          <t>大於 50%</t>
+        </is>
       </c>
       <c r="AK11" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 quanta/dist/20261025_廣達模型_v0.2.xlsx Val!B123；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 quanta/dist/20261025_廣達模型_v0.2.1.xlsx Val!B123；投資建議 quanta/dist/20261025_廣達模型_v0.2.1.xlsx Val!B136；級距 quanta/dist/20261025_廣達模型_v0.2.1.xlsx Val!B135</t>
         </is>
       </c>
     </row>
@@ -9187,7 +9207,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ibiden/dist/20261025_Ibiden模型_v0.2.xlsx Val!B96</t>
+          <t>ibiden/dist/20261025_Ibiden模型_v0.2.1.xlsx Val!B96</t>
         </is>
       </c>
       <c r="J12" s="4" t="n">
@@ -9195,7 +9215,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>ibiden/dist/20261025_Ibiden模型_v0.2.xlsx Val!D80</t>
+          <t>ibiden/dist/20261025_Ibiden模型_v0.2.1.xlsx Val!D80</t>
         </is>
       </c>
       <c r="N12">
@@ -9217,9 +9237,10 @@
         <f>P12/N12-1</f>
         <v/>
       </c>
-      <c r="S12">
-        <f>IF(Q12&gt;0.5,"強力買進",IF(Q12&gt;0.25,"買進",IF(Q12&gt;=-0.25,"中立",IF(Q12&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S12" s="4" t="inlineStr">
+        <is>
+          <t>放空</t>
+        </is>
       </c>
       <c r="T12">
         <f>9531.45203105499/N12-1</f>
@@ -9271,7 +9292,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>[Derived] ibiden/dist/20261025_Ibiden模型_v0.2.xlsx PL!D11…PL!G33</t>
+          <t>[Derived] ibiden/dist/20261025_Ibiden模型_v0.2.1.xlsx PL!D11…PL!G33</t>
         </is>
       </c>
       <c r="AH12">
@@ -9282,13 +9303,14 @@
         <f>IF(S12="未上市","未上市",IF(AND(AH12="不通過",OR(S12="強力買進",S12="買進",S12="未估值")),"收支不足",S12))</f>
         <v/>
       </c>
-      <c r="AJ12">
-        <f>IF(Q12&gt;0.5,"大於 50%",IF(Q12&gt;0.25,"25%–50%",IF(Q12&gt;=0,"0%–25%",IF(Q12&gt;=-0.25,"0%～−25%",IF(Q12&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ12" s="4" t="inlineStr">
+        <is>
+          <t>−25%～−50%</t>
+        </is>
       </c>
       <c r="AK12" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 ibiden/dist/20261025_Ibiden模型_v0.2.xlsx Val!B99；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 ibiden/dist/20261025_Ibiden模型_v0.2.1.xlsx Val!B99；投資建議 ibiden/dist/20261025_Ibiden模型_v0.2.1.xlsx Val!B110；級距 ibiden/dist/20261025_Ibiden模型_v0.2.1.xlsx Val!B109</t>
         </is>
       </c>
     </row>
@@ -9322,7 +9344,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>advantest/dist/20261025_Advantest模型_v0.3.xlsx Val!B146</t>
+          <t>advantest/dist/20261025_Advantest模型_v0.3.1.xlsx Val!B146</t>
         </is>
       </c>
       <c r="J13" s="4" t="n">
@@ -9330,7 +9352,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>advantest/dist/20261025_Advantest模型_v0.3.xlsx Val!D130</t>
+          <t>advantest/dist/20261025_Advantest模型_v0.3.1.xlsx Val!D130</t>
         </is>
       </c>
       <c r="N13">
@@ -9352,9 +9374,10 @@
         <f>P13/N13-1</f>
         <v/>
       </c>
-      <c r="S13">
-        <f>IF(Q13&gt;0.5,"強力買進",IF(Q13&gt;0.25,"買進",IF(Q13&gt;=-0.25,"中立",IF(Q13&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>放空</t>
+        </is>
       </c>
       <c r="T13">
         <f>24494.453736442/N13-1</f>
@@ -9401,7 +9424,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>[Derived] advantest/dist/20261025_Advantest模型_v0.3.xlsx PL!D12…PL!G34</t>
+          <t>[Derived] advantest/dist/20261025_Advantest模型_v0.3.1.xlsx PL!D12…PL!G34</t>
         </is>
       </c>
       <c r="AH13">
@@ -9412,13 +9435,14 @@
         <f>IF(S13="未上市","未上市",IF(AND(AH13="不通過",OR(S13="強力買進",S13="買進",S13="未估值")),"收支不足",S13))</f>
         <v/>
       </c>
-      <c r="AJ13">
-        <f>IF(Q13&gt;0.5,"大於 50%",IF(Q13&gt;0.25,"25%–50%",IF(Q13&gt;=0,"0%–25%",IF(Q13&gt;=-0.25,"0%～−25%",IF(Q13&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ13" s="4" t="inlineStr">
+        <is>
+          <t>−25%～−50%</t>
+        </is>
       </c>
       <c r="AK13" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 advantest/dist/20261025_Advantest模型_v0.3.xlsx Val!B149；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 advantest/dist/20261025_Advantest模型_v0.3.1.xlsx Val!B149；投資建議 advantest/dist/20261025_Advantest模型_v0.3.1.xlsx Val!B158；級距 advantest/dist/20261025_Advantest模型_v0.3.1.xlsx Val!B157</t>
         </is>
       </c>
     </row>
@@ -9452,7 +9476,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>disco/dist/20261025_Disco模型_v0.2.1.xlsx Val!B107</t>
+          <t>disco/dist/20261025_Disco模型_v0.2.2.xlsx Val!B107</t>
         </is>
       </c>
       <c r="J14" s="4" t="n">
@@ -9460,7 +9484,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>disco/dist/20261025_Disco模型_v0.2.1.xlsx Val!D91</t>
+          <t>disco/dist/20261025_Disco模型_v0.2.2.xlsx Val!D91</t>
         </is>
       </c>
       <c r="N14">
@@ -9482,9 +9506,10 @@
         <f>P14/N14-1</f>
         <v/>
       </c>
-      <c r="S14">
-        <f>IF(Q14&gt;0.5,"強力買進",IF(Q14&gt;0.25,"買進",IF(Q14&gt;=-0.25,"中立",IF(Q14&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S14" s="4" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
       </c>
       <c r="T14">
         <f>45104.6418701108/N14-1</f>
@@ -9531,7 +9556,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>[Derived] disco/dist/20261025_Disco模型_v0.2.1.xlsx PL!D16…PL!G52</t>
+          <t>[Derived] disco/dist/20261025_Disco模型_v0.2.2.xlsx PL!D16…PL!G52</t>
         </is>
       </c>
       <c r="AH14">
@@ -9542,13 +9567,14 @@
         <f>IF(S14="未上市","未上市",IF(AND(AH14="不通過",OR(S14="強力買進",S14="買進",S14="未估值")),"收支不足",S14))</f>
         <v/>
       </c>
-      <c r="AJ14">
-        <f>IF(Q14&gt;0.5,"大於 50%",IF(Q14&gt;0.25,"25%–50%",IF(Q14&gt;=0,"0%–25%",IF(Q14&gt;=-0.25,"0%～−25%",IF(Q14&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ14" s="4" t="inlineStr">
+        <is>
+          <t>0%～−25%</t>
+        </is>
       </c>
       <c r="AK14" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 disco/dist/20261025_Disco模型_v0.2.1.xlsx Val!B110；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 disco/dist/20261025_Disco模型_v0.2.2.xlsx Val!B110；投資建議 disco/dist/20261025_Disco模型_v0.2.2.xlsx Val!B119；級距 disco/dist/20261025_Disco模型_v0.2.2.xlsx Val!B118</t>
         </is>
       </c>
     </row>
@@ -9574,31 +9600,23 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>模型加權目標價</t>
+          <t>加權目標價（DCF 50%＋分部加總 50%）</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>359.058838816622</v>
+        <v>388.947955859393</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>microsoft/dist/20261025_Microsoft收支模型_v0_2_2.xlsx 摘要!C7</t>
+          <t>microsoft/dist/20261027_Microsoft個股模型_v0.3.xlsx Val!B36</t>
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>359.058838816622</v>
+        <v>298.502438692235</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>microsoft/dist/20261025_Microsoft收支模型_v0_2_2.xlsx 摘要!C7</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="n">
-        <v>360.157606985669</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>microsoft/dist/20261025_Microsoft收支模型_v0_2_2.xlsx 摘要!C10</t>
+          <t>microsoft/dist/20261027_Microsoft個股模型_v0.3.xlsx Val!D13</t>
         </is>
       </c>
       <c r="N15">
@@ -9613,21 +9631,26 @@
         <f>MIN(J15,L15)</f>
         <v/>
       </c>
-      <c r="Q15">
-        <f>O15/N15-1</f>
-        <v/>
+      <c r="Q15" s="4" t="n">
+        <v>-0.269718445626375</v>
       </c>
       <c r="R15">
         <f>P15/N15-1</f>
         <v/>
       </c>
-      <c r="S15">
-        <f>IF(Q15&gt;0.5,"強力買進",IF(Q15&gt;0.25,"買進",IF(Q15&gt;=-0.25,"中立",IF(Q15&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>放空</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>20.5 ／ 21.6 ／ 23.0</t>
+        </is>
       </c>
       <c r="W15" s="1" t="inlineStr">
         <is>
-          <t>模型點位 $359.1（模型日現價 $529.76）；情境區間 $360.2–$380.6，方法區間 $353.5–$359.1｜MAG 模型終值占 EV 逾 90%，評價口徑待 MAG v0.3</t>
+          <t>DCF 目標價 342.2（Val!B14）；Comparable 目標價 435.7（Val!B31）；市場共識目標價 603.4（Val!B38，外部、僅供對照）；價格帶 C～A 情境 DCF 298.5～382.1</t>
         </is>
       </c>
       <c r="Z15">
@@ -9645,23 +9668,23 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>營運缺口＋股利＋回購</t>
+          <t>自由現金流扣股利五年合計（情境 A／B／C）</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>FY27 -7.8、FY28 27.7、FY29 70.2、FY30 76.7、FY31 11.2</t>
+          <t>A 378.6、B 274.0、C 151.4</t>
         </is>
       </c>
       <c r="AE15" s="4" t="n">
-        <v>178.0401267004849</v>
+        <v>803.952086236789</v>
       </c>
       <c r="AF15" s="4" t="n">
-        <v>-7.831738650858899</v>
+        <v>151.420119937449</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>[Derived] microsoft/dist/20261025_Microsoft收支模型_v0_2_2.xlsx 各期收支!C54＋C23＋C24…各期收支!G54＋G23＋G24</t>
+          <t>[Derived] microsoft/dist/20261027_Microsoft個股模型_v0.3.xlsx CF!B5…CF!D5</t>
         </is>
       </c>
       <c r="AH15">
@@ -9672,13 +9695,14 @@
         <f>IF(S15="未上市","未上市",IF(AND(AH15="不通過",OR(S15="強力買進",S15="買進",S15="未估值")),"收支不足",S15))</f>
         <v/>
       </c>
-      <c r="AJ15">
-        <f>IF(Q15&gt;0.5,"大於 50%",IF(Q15&gt;0.25,"25%–50%",IF(Q15&gt;=0,"0%–25%",IF(Q15&gt;=-0.25,"0%～−25%",IF(Q15&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>上檔空間＝模型加權目標價 microsoft/dist/20261025_Microsoft收支模型_v0_2_2.xlsx 摘要!C7 ÷ 外部收盤價 − 1，依本地圖五級規則自算（模型自身評等以模型日價計、級距不同，不採用；原值見模型摘要頁）</t>
+      <c r="AJ15" s="4" t="inlineStr">
+        <is>
+          <t>−25%～−50%</t>
+        </is>
+      </c>
+      <c r="AK15" s="1" t="inlineStr">
+        <is>
+          <t>上檔空間 microsoft/dist/20261027_Microsoft個股模型_v0.3.xlsx Val!B40；投資建議 microsoft/dist/20261027_Microsoft個股模型_v0.3.xlsx Val!B43；級距 microsoft/dist/20261027_Microsoft個股模型_v0.3.xlsx Val!B42</t>
         </is>
       </c>
     </row>
@@ -9704,31 +9728,23 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>模型加權目標價</t>
+          <t>加權目標價（DCF 50%＋分部加總 50%）</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>201.7143092677</v>
+        <v>210.788175534535</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>amazon/dist/20261025_Amazon收支模型_v0_2_2.xlsx 摘要!C7</t>
+          <t>amazon/dist/20261027_Amazon個股模型_v0.3.xlsx Val!B19</t>
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>201.7143092677</v>
+        <v>118.729987132669</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>amazon/dist/20261025_Amazon收支模型_v0_2_2.xlsx 摘要!C7</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="n">
-        <v>201.136157296701</v>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>amazon/dist/20261025_Amazon收支模型_v0_2_2.xlsx 摘要!C10</t>
+          <t>amazon/dist/20261027_Amazon個股模型_v0.3.xlsx Val!D5</t>
         </is>
       </c>
       <c r="N16">
@@ -9743,21 +9759,21 @@
         <f>MIN(J16,L16)</f>
         <v/>
       </c>
-      <c r="Q16">
-        <f>O16/N16-1</f>
-        <v/>
+      <c r="Q16" s="4" t="n">
+        <v>-0.153767009777449</v>
       </c>
       <c r="R16">
         <f>P16/N16-1</f>
         <v/>
       </c>
-      <c r="S16">
-        <f>IF(Q16&gt;0.5,"強力買進",IF(Q16&gt;0.25,"買進",IF(Q16&gt;=-0.25,"中立",IF(Q16&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S16" s="4" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
       </c>
       <c r="W16" s="1" t="inlineStr">
         <is>
-          <t>模型點位 $201.7（模型日現價 $259.92）；情境區間 $201.1–$212.3，方法區間 $197.5–$201.7｜MAG 模型終值占 EV 逾 90%，評價口徑待 MAG v0.3</t>
+          <t>DCF 目標價 150.7（Val!B17）；Comparable 目標價 270.8（Val!B18）；市場共識目標價 332.2（Val!B25，外部、僅供對照）；價格帶 C～A 情境 DCF 118.7～205.6</t>
         </is>
       </c>
       <c r="Z16">
@@ -9775,23 +9791,23 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>營運缺口＋股利＋回購</t>
+          <t>自由現金流扣股利五年合計（情境 A／B／C）</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2026 -122.8、2027 -71.8、2028 -34.2、2029 6.1、2030 -70.1</t>
+          <t>A 192.9、B 10.2、C -51.6</t>
         </is>
       </c>
       <c r="AE16" s="4" t="n">
-        <v>-292.8415771813029</v>
+        <v>151.5243350124342</v>
       </c>
       <c r="AF16" s="4" t="n">
-        <v>-122.819739543556</v>
+        <v>-51.5941543670482</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>[Derived] amazon/dist/20261025_Amazon收支模型_v0_2_2.xlsx 各期收支!C54＋C23＋C24…各期收支!G54＋G23＋G24</t>
+          <t>[Derived] amazon/dist/20261027_Amazon個股模型_v0.3.xlsx CF!B6…CF!D6</t>
         </is>
       </c>
       <c r="AH16">
@@ -9802,13 +9818,14 @@
         <f>IF(S16="未上市","未上市",IF(AND(AH16="不通過",OR(S16="強力買進",S16="買進",S16="未估值")),"收支不足",S16))</f>
         <v/>
       </c>
-      <c r="AJ16">
-        <f>IF(Q16&gt;0.5,"大於 50%",IF(Q16&gt;0.25,"25%–50%",IF(Q16&gt;=0,"0%–25%",IF(Q16&gt;=-0.25,"0%～−25%",IF(Q16&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>上檔空間＝模型加權目標價 amazon/dist/20261025_Amazon收支模型_v0_2_2.xlsx 摘要!C7 ÷ 外部收盤價 − 1，依本地圖五級規則自算（模型自身評等以模型日價計、級距不同，不採用；原值見模型摘要頁）</t>
+      <c r="AJ16" s="4" t="inlineStr">
+        <is>
+          <t>0%～−25%</t>
+        </is>
+      </c>
+      <c r="AK16" s="1" t="inlineStr">
+        <is>
+          <t>上檔空間 amazon/dist/20261027_Amazon個股模型_v0.3.xlsx Val!B21；投資建議 amazon/dist/20261027_Amazon個股模型_v0.3.xlsx Val!B24；級距 amazon/dist/20261027_Amazon個股模型_v0.3.xlsx Val!B23</t>
         </is>
       </c>
     </row>
@@ -9834,31 +9851,23 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>模型加權目標價</t>
+          <t>加權目標價（DCF 50%＋分部加總 50%）</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>146.09287356031</v>
+        <v>251.682246082838</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>alphabet/dist/20261025_Alphabet收支模型_v0_2_2.xlsx 摘要!C7</t>
+          <t>alphabet/dist/20261027_Alphabet個股模型_v0.3.xlsx Val!B8</t>
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>146.09287356031</v>
+        <v>143.260133369341</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>alphabet/dist/20261025_Alphabet收支模型_v0_2_2.xlsx 摘要!C7</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v>122.889116020962</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>alphabet/dist/20261025_Alphabet收支模型_v0_2_2.xlsx 摘要!C10</t>
+          <t>alphabet/dist/20261027_Alphabet個股模型_v0.3.xlsx Val!D102</t>
         </is>
       </c>
       <c r="N17">
@@ -9873,21 +9882,21 @@
         <f>MIN(J17,L17)</f>
         <v/>
       </c>
-      <c r="Q17">
-        <f>O17/N17-1</f>
-        <v/>
+      <c r="Q17" s="4" t="n">
+        <v>-0.205548465647608</v>
       </c>
       <c r="R17">
         <f>P17/N17-1</f>
         <v/>
       </c>
-      <c r="S17">
-        <f>IF(Q17&gt;0.5,"強力買進",IF(Q17&gt;0.25,"買進",IF(Q17&gt;=-0.25,"中立",IF(Q17&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
       </c>
       <c r="W17" s="1" t="inlineStr">
         <is>
-          <t>模型點位 $146.1（模型日現價 $350.50）；情境區間 $122.9–$175.1，方法區間 $144.1–$146.1｜MAG 模型終值占 EV 逾 90%，評價口徑待 MAG v0.3</t>
+          <t>DCF 目標價 184.6（Val!B6）；Comparable 目標價 318.8（Val!B7）；市場共識目標價 429.1（Val!B10，外部、僅供對照）；價格帶 C～A 情境 DCF 143.3～215.5</t>
         </is>
       </c>
       <c r="Z17">
@@ -9905,23 +9914,23 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>營運缺口＋股利＋回購</t>
+          <t>自由現金流扣股利五年合計（情境 A／B／C）</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>2026 -62.0、2027 -11.4、2028 10.9、2029 23.1、2030 -67.6</t>
+          <t>A 261.2、B 180.1、C 29.8</t>
         </is>
       </c>
       <c r="AE17" s="4" t="n">
-        <v>-106.9279391300797</v>
+        <v>471.1174088146958</v>
       </c>
       <c r="AF17" s="4" t="n">
-        <v>-67.601689194111</v>
+        <v>29.8478349489597</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>[Derived] alphabet/dist/20261025_Alphabet收支模型_v0_2_2.xlsx 各期收支!C54＋C23＋C24…各期收支!G54＋G23＋G24</t>
+          <t>[Derived] alphabet/dist/20261027_Alphabet個股模型_v0.3.xlsx CF!B6…CF!D6</t>
         </is>
       </c>
       <c r="AH17">
@@ -9932,13 +9941,14 @@
         <f>IF(S17="未上市","未上市",IF(AND(AH17="不通過",OR(S17="強力買進",S17="買進",S17="未估值")),"收支不足",S17))</f>
         <v/>
       </c>
-      <c r="AJ17">
-        <f>IF(Q17&gt;0.5,"大於 50%",IF(Q17&gt;0.25,"25%–50%",IF(Q17&gt;=0,"0%–25%",IF(Q17&gt;=-0.25,"0%～−25%",IF(Q17&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>上檔空間＝模型加權目標價 alphabet/dist/20261025_Alphabet收支模型_v0_2_2.xlsx 摘要!C7 ÷ 外部收盤價 − 1，依本地圖五級規則自算（模型自身評等以模型日價計、級距不同，不採用；原值見模型摘要頁）</t>
+      <c r="AJ17" s="4" t="inlineStr">
+        <is>
+          <t>0%～−25%</t>
+        </is>
+      </c>
+      <c r="AK17" s="1" t="inlineStr">
+        <is>
+          <t>上檔空間 alphabet/dist/20261027_Alphabet個股模型_v0.3.xlsx Val!B11；投資建議 alphabet/dist/20261027_Alphabet個股模型_v0.3.xlsx Val!B14；級距 alphabet/dist/20261027_Alphabet個股模型_v0.3.xlsx Val!B13</t>
         </is>
       </c>
     </row>
@@ -9964,31 +9974,23 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>模型加權目標價</t>
+          <t>加權目標價（DCF 50%＋分部加總 50%）</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>84.2399682943779</v>
+        <v>73.2244042213954</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>oracle/dist/20261022_Oracle收支模型_v0_3_1.xlsx 摘要!C7</t>
+          <t>oracle/dist/20261027_Oracle個股模型_v0.4.xlsx Val!C74</t>
         </is>
       </c>
       <c r="J18" s="4" t="n">
-        <v>84.2399682943779</v>
+        <v>17.1600249327927</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>oracle/dist/20261022_Oracle收支模型_v0_3_1.xlsx 摘要!C7</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v>77.41468872947129</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>oracle/dist/20261022_Oracle收支模型_v0_3_1.xlsx 摘要!C10</t>
+          <t>oracle/dist/20261027_Oracle個股模型_v0.4.xlsx Val!E30</t>
         </is>
       </c>
       <c r="N18">
@@ -10003,21 +10005,21 @@
         <f>MIN(J18,L18)</f>
         <v/>
       </c>
-      <c r="Q18">
-        <f>O18/N18-1</f>
-        <v/>
+      <c r="Q18" s="4" t="n">
+        <v>-0.419130539255946</v>
       </c>
       <c r="R18">
         <f>P18/N18-1</f>
         <v/>
       </c>
-      <c r="S18">
-        <f>IF(Q18&gt;0.5,"強力買進",IF(Q18&gt;0.25,"買進",IF(Q18&gt;=-0.25,"中立",IF(Q18&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S18" s="4" t="inlineStr">
+        <is>
+          <t>放空</t>
+        </is>
       </c>
       <c r="W18" s="1" t="inlineStr">
         <is>
-          <t>模型點位 $84.2（模型日現價 $129.13）；情境區間 $77.4–$91.9，方法區間 $78.7–$84.2</t>
+          <t>DCF 目標價 41.7（Val!C72）；Comparable 目標價 104.7（Val!C73）；市場共識目標價 237.4（Val!C76，外部、僅供對照）；價格帶 C～A 情境 DCF 17.2～57.1</t>
         </is>
       </c>
       <c r="Z18">
@@ -10035,23 +10037,23 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>營運缺口＋股利</t>
+          <t>自由現金流扣股利五年合計（情境 A／B／C）</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>FY27 -25.8、FY28 -21.1、FY29 23.7、FY30 9.7、FY31 8.1</t>
+          <t>A 111.1、B 72.8、C 8.4</t>
         </is>
       </c>
       <c r="AE18" s="4" t="n">
-        <v>-5.431099371743606</v>
+        <v>192.1804689163291</v>
       </c>
       <c r="AF18" s="4" t="n">
-        <v>-25.8031832210438</v>
+        <v>8.353477656004481</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>[Derived] oracle/dist/20261022_Oracle收支模型_v0_3_1.xlsx 各期收支!C50＋C23…各期收支!G50＋G23</t>
+          <t>[Derived] oracle/dist/20261027_Oracle個股模型_v0.4.xlsx CF!C4…CF!E4</t>
         </is>
       </c>
       <c r="AH18">
@@ -10062,13 +10064,14 @@
         <f>IF(S18="未上市","未上市",IF(AND(AH18="不通過",OR(S18="強力買進",S18="買進",S18="未估值")),"收支不足",S18))</f>
         <v/>
       </c>
-      <c r="AJ18">
-        <f>IF(Q18&gt;0.5,"大於 50%",IF(Q18&gt;0.25,"25%–50%",IF(Q18&gt;=0,"0%–25%",IF(Q18&gt;=-0.25,"0%～−25%",IF(Q18&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>上檔空間＝模型加權目標價 oracle/dist/20261022_Oracle收支模型_v0_3_1.xlsx 摘要!C7 ÷ 外部收盤價 − 1，依本地圖五級規則自算（模型自身評等以模型日價計、級距不同，不採用；原值見模型摘要頁）</t>
+      <c r="AJ18" s="4" t="inlineStr">
+        <is>
+          <t>−25%～−50%</t>
+        </is>
+      </c>
+      <c r="AK18" s="1" t="inlineStr">
+        <is>
+          <t>上檔空間 oracle/dist/20261027_Oracle個股模型_v0.4.xlsx Val!C77；投資建議 oracle/dist/20261027_Oracle個股模型_v0.4.xlsx Val!C80；級距 oracle/dist/20261027_Oracle個股模型_v0.4.xlsx Val!C79</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10235,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>nebius/dist/20261022_Nebius收支模型_v0_5.xlsx 摘要!C7</t>
+          <t>nebius/dist/20261022_Nebius收支模型_v0_5_1.xlsx 摘要!C7</t>
         </is>
       </c>
       <c r="J20" s="4" t="n">
@@ -10240,7 +10243,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>nebius/dist/20261022_Nebius收支模型_v0_5.xlsx 摘要!C7</t>
+          <t>nebius/dist/20261022_Nebius收支模型_v0_5_1.xlsx 摘要!C7</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
@@ -10248,7 +10251,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>nebius/dist/20261022_Nebius收支模型_v0_5.xlsx 摘要!C10</t>
+          <t>nebius/dist/20261022_Nebius收支模型_v0_5_1.xlsx 摘要!C10</t>
         </is>
       </c>
       <c r="N20">
@@ -10311,7 +10314,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>[Derived] nebius/dist/20261022_Nebius收支模型_v0_5.xlsx 各期收支!C45…各期收支!G45</t>
+          <t>[Derived] nebius/dist/20261022_Nebius收支模型_v0_5_1.xlsx 各期收支!C45…各期收支!G45</t>
         </is>
       </c>
       <c r="AH20">
@@ -10328,7 +10331,7 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>上檔空間＝模型加權目標價 nebius/dist/20261022_Nebius收支模型_v0_5.xlsx 摘要!C7 ÷ 外部收盤價 − 1，依本地圖五級規則自算（模型自身評等以模型日價計、級距不同，不採用；原值見模型摘要頁）</t>
+          <t>上檔空間＝模型加權目標價 nebius/dist/20261022_Nebius收支模型_v0_5_1.xlsx 摘要!C7 ÷ 外部收盤價 − 1，依本地圖五級規則自算（模型自身評等以模型日價計、級距不同，不採用；原值見模型摘要頁）</t>
         </is>
       </c>
     </row>
@@ -10861,7 +10864,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>amd/dist/20261025_AMD模型_v0.2.1.xlsx Val!B40</t>
+          <t>amd/dist/20261025_AMD模型_v0.2.2.xlsx Val!B40</t>
         </is>
       </c>
       <c r="J26" s="4" t="n">
@@ -10869,7 +10872,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>amd/dist/20261025_AMD模型_v0.2.1.xlsx Val!B47</t>
+          <t>amd/dist/20261025_AMD模型_v0.2.2.xlsx Val!B47</t>
         </is>
       </c>
       <c r="N26">
@@ -10891,9 +10894,10 @@
         <f>P26/N26-1</f>
         <v/>
       </c>
-      <c r="S26">
-        <f>IF(Q26&gt;0.5,"強力買進",IF(Q26&gt;0.25,"買進",IF(Q26&gt;=-0.25,"中立",IF(Q26&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S26" s="4" t="inlineStr">
+        <is>
+          <t>強力放空</t>
+        </is>
       </c>
       <c r="T26">
         <f>471.572606000429/N26-1</f>
@@ -10945,7 +10949,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>[Derived] amd/dist/20261025_AMD模型_v0.2.1.xlsx PL!D15…PL!G47</t>
+          <t>[Derived] amd/dist/20261025_AMD模型_v0.2.2.xlsx PL!D15…PL!G47</t>
         </is>
       </c>
       <c r="AH26">
@@ -10956,13 +10960,14 @@
         <f>IF(S26="未上市","未上市",IF(AND(AH26="不通過",OR(S26="強力買進",S26="買進",S26="未估值")),"收支不足",S26))</f>
         <v/>
       </c>
-      <c r="AJ26">
-        <f>IF(Q26&gt;0.5,"大於 50%",IF(Q26&gt;0.25,"25%–50%",IF(Q26&gt;=0,"0%–25%",IF(Q26&gt;=-0.25,"0%～−25%",IF(Q26&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ26" s="4" t="inlineStr">
+        <is>
+          <t>小於 −50%</t>
+        </is>
       </c>
       <c r="AK26" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 amd/dist/20261025_AMD模型_v0.2.1.xlsx Val!B43；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 amd/dist/20261025_AMD模型_v0.2.2.xlsx Val!B43；投資建議 amd/dist/20261025_AMD模型_v0.2.2.xlsx Val!B177；級距 amd/dist/20261025_AMD模型_v0.2.2.xlsx Val!B176</t>
         </is>
       </c>
     </row>
@@ -10996,7 +11001,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>mediatek/dist/20261025_聯發科模型_v0.1.xlsx Val!B39</t>
+          <t>mediatek/dist/20261025_聯發科模型_v0.1.1.xlsx Val!B39</t>
         </is>
       </c>
       <c r="J27" s="4" t="n">
@@ -11004,7 +11009,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>mediatek/dist/20261025_聯發科模型_v0.1.xlsx Val!D23</t>
+          <t>mediatek/dist/20261025_聯發科模型_v0.1.1.xlsx Val!D23</t>
         </is>
       </c>
       <c r="N27">
@@ -11026,9 +11031,10 @@
         <f>P27/N27-1</f>
         <v/>
       </c>
-      <c r="S27">
-        <f>IF(Q27&gt;0.5,"強力買進",IF(Q27&gt;0.25,"買進",IF(Q27&gt;=-0.25,"中立",IF(Q27&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S27" s="4" t="inlineStr">
+        <is>
+          <t>放空</t>
+        </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -11071,7 +11077,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>[Derived] mediatek/dist/20261025_聯發科模型_v0.1.xlsx PL!D13…PL!J41</t>
+          <t>[Derived] mediatek/dist/20261025_聯發科模型_v0.1.1.xlsx PL!D13…PL!J41</t>
         </is>
       </c>
       <c r="AH27">
@@ -11082,13 +11088,14 @@
         <f>IF(S27="未上市","未上市",IF(AND(AH27="不通過",OR(S27="強力買進",S27="買進",S27="未估值")),"收支不足",S27))</f>
         <v/>
       </c>
-      <c r="AJ27">
-        <f>IF(Q27&gt;0.5,"大於 50%",IF(Q27&gt;0.25,"25%–50%",IF(Q27&gt;=0,"0%–25%",IF(Q27&gt;=-0.25,"0%～−25%",IF(Q27&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ27" s="4" t="inlineStr">
+        <is>
+          <t>−25%～−50%</t>
+        </is>
       </c>
       <c r="AK27" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 mediatek/dist/20261025_聯發科模型_v0.1.xlsx Val!B42；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 mediatek/dist/20261025_聯發科模型_v0.1.1.xlsx Val!B42；投資建議 mediatek/dist/20261025_聯發科模型_v0.1.1.xlsx Val!B135；級距 mediatek/dist/20261025_聯發科模型_v0.1.1.xlsx Val!B134</t>
         </is>
       </c>
     </row>
@@ -11118,19 +11125,19 @@
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>128.033003490757</v>
+        <v>126.964605060311</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>mrvl/dist/20261025_邁威爾模型_v0.2.xlsx Val!B40</t>
+          <t>mrvl/dist/20261026_邁威爾模型_v0.2.2.xlsx Val!B40</t>
         </is>
       </c>
       <c r="J28" s="4" t="n">
-        <v>71.0382339875876</v>
+        <v>71.8838596724305</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>mrvl/dist/20261025_邁威爾模型_v0.2.xlsx Val!B47</t>
+          <t>mrvl/dist/20261026_邁威爾模型_v0.2.2.xlsx Val!B47</t>
         </is>
       </c>
       <c r="N28">
@@ -11146,18 +11153,19 @@
         <v/>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.439705030454872</v>
+        <v>-0.44438053012861</v>
       </c>
       <c r="R28">
         <f>P28/N28-1</f>
         <v/>
       </c>
-      <c r="S28">
-        <f>IF(Q28&gt;0.5,"強力買進",IF(Q28&gt;0.25,"買進",IF(Q28&gt;=-0.25,"中立",IF(Q28&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S28" s="4" t="inlineStr">
+        <is>
+          <t>放空</t>
+        </is>
       </c>
       <c r="T28">
-        <f>203.164070486016/N28-1</f>
+        <f>202.512511941354/N28-1</f>
         <v/>
       </c>
       <c r="U28" t="inlineStr">
@@ -11167,12 +11175,12 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>35.1 ／ 35.1 ／ 35.1</t>
+          <t>35.5 ／ 35.1 ／ 34.8</t>
         </is>
       </c>
       <c r="W28" s="1" t="inlineStr">
         <is>
-          <t>DCF 目標價 116.4（Val!B23）；Comparable 目標價 139.6（Val!B41）；市場共識目標價 341.4（Val!B42，外部、僅供對照）；價格帶 C～A 情境 DCF 71.0～147.4</t>
+          <t>DCF 目標價 115.2（Val!B23）；Comparable 目標價 138.8（Val!B41）；市場共識目標價 341.4（Val!B42，外部、僅供對照）；價格帶 C～A 情境 DCF 71.9～142.6</t>
         </is>
       </c>
       <c r="Z28">
@@ -11195,18 +11203,18 @@
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>8 個情境年度淨利（不含實績），全部為正</t>
+          <t>10 個情境年度淨利（不含實績），全部為正</t>
         </is>
       </c>
       <c r="AE28" s="4" t="n">
-        <v>52.61793498372541</v>
+        <v>64.19063650443796</v>
       </c>
       <c r="AF28" s="4" t="n">
         <v>3.83971098</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>[Derived] mrvl/dist/20261025_邁威爾模型_v0.2.xlsx PL!D13…PL!G39</t>
+          <t>[Derived] mrvl/dist/20261026_邁威爾模型_v0.2.2.xlsx PL!D13…PL!G39</t>
         </is>
       </c>
       <c r="AH28">
@@ -11217,13 +11225,14 @@
         <f>IF(S28="未上市","未上市",IF(AND(AH28="不通過",OR(S28="強力買進",S28="買進",S28="未估值")),"收支不足",S28))</f>
         <v/>
       </c>
-      <c r="AJ28">
-        <f>IF(Q28&gt;0.5,"大於 50%",IF(Q28&gt;0.25,"25%–50%",IF(Q28&gt;=0,"0%–25%",IF(Q28&gt;=-0.25,"0%～−25%",IF(Q28&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ28" s="4" t="inlineStr">
+        <is>
+          <t>−25%～−50%</t>
+        </is>
       </c>
       <c r="AK28" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 mrvl/dist/20261025_邁威爾模型_v0.2.xlsx Val!B43；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 mrvl/dist/20261026_邁威爾模型_v0.2.2.xlsx Val!B43；投資建議 mrvl/dist/20261026_邁威爾模型_v0.2.2.xlsx Val!B151；級距 mrvl/dist/20261026_邁威爾模型_v0.2.2.xlsx Val!B150</t>
         </is>
       </c>
     </row>
@@ -11257,7 +11266,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>alchip/dist/20261025_世芯-KY模型_v0.1.xlsx Val!B39</t>
+          <t>alchip/dist/20261025_世芯-KY模型_v0.1.1.xlsx Val!B39</t>
         </is>
       </c>
       <c r="J29" s="4" t="n">
@@ -11265,7 +11274,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>alchip/dist/20261025_世芯-KY模型_v0.1.xlsx Val!D23</t>
+          <t>alchip/dist/20261025_世芯-KY模型_v0.1.1.xlsx Val!D23</t>
         </is>
       </c>
       <c r="N29">
@@ -11287,9 +11296,10 @@
         <f>P29/N29-1</f>
         <v/>
       </c>
-      <c r="S29">
-        <f>IF(Q29&gt;0.5,"強力買進",IF(Q29&gt;0.25,"買進",IF(Q29&gt;=-0.25,"中立",IF(Q29&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S29" s="4" t="inlineStr">
+        <is>
+          <t>強力買進</t>
+        </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -11332,7 +11342,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>[Derived] alchip/dist/20261025_世芯-KY模型_v0.1.xlsx PL!D11…PL!J35</t>
+          <t>[Derived] alchip/dist/20261025_世芯-KY模型_v0.1.1.xlsx PL!D11…PL!J35</t>
         </is>
       </c>
       <c r="AH29">
@@ -11343,13 +11353,14 @@
         <f>IF(S29="未上市","未上市",IF(AND(AH29="不通過",OR(S29="強力買進",S29="買進",S29="未估值")),"收支不足",S29))</f>
         <v/>
       </c>
-      <c r="AJ29">
-        <f>IF(Q29&gt;0.5,"大於 50%",IF(Q29&gt;0.25,"25%–50%",IF(Q29&gt;=0,"0%–25%",IF(Q29&gt;=-0.25,"0%～−25%",IF(Q29&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ29" s="4" t="inlineStr">
+        <is>
+          <t>大於 50%</t>
+        </is>
       </c>
       <c r="AK29" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 alchip/dist/20261025_世芯-KY模型_v0.1.xlsx Val!B42；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 alchip/dist/20261025_世芯-KY模型_v0.1.1.xlsx Val!B42；投資建議 alchip/dist/20261025_世芯-KY模型_v0.1.1.xlsx Val!B135；級距 alchip/dist/20261025_世芯-KY模型_v0.1.1.xlsx Val!B134</t>
         </is>
       </c>
     </row>
@@ -11383,7 +11394,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>guc/dist/20261025_創意模型_v0.1.xlsx Val!B39</t>
+          <t>guc/dist/20261025_創意模型_v0.1.1.xlsx Val!B39</t>
         </is>
       </c>
       <c r="J30" s="4" t="n">
@@ -11391,7 +11402,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>guc/dist/20261025_創意模型_v0.1.xlsx Val!D23</t>
+          <t>guc/dist/20261025_創意模型_v0.1.1.xlsx Val!D23</t>
         </is>
       </c>
       <c r="N30">
@@ -11413,9 +11424,10 @@
         <f>P30/N30-1</f>
         <v/>
       </c>
-      <c r="S30">
-        <f>IF(Q30&gt;0.5,"強力買進",IF(Q30&gt;0.25,"買進",IF(Q30&gt;=-0.25,"中立",IF(Q30&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S30" s="4" t="inlineStr">
+        <is>
+          <t>強力放空</t>
+        </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -11458,7 +11470,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>[Derived] guc/dist/20261025_創意模型_v0.1.xlsx PL!D13…PL!J41</t>
+          <t>[Derived] guc/dist/20261025_創意模型_v0.1.1.xlsx PL!D13…PL!J41</t>
         </is>
       </c>
       <c r="AH30">
@@ -11469,13 +11481,14 @@
         <f>IF(S30="未上市","未上市",IF(AND(AH30="不通過",OR(S30="強力買進",S30="買進",S30="未估值")),"收支不足",S30))</f>
         <v/>
       </c>
-      <c r="AJ30">
-        <f>IF(Q30&gt;0.5,"大於 50%",IF(Q30&gt;0.25,"25%–50%",IF(Q30&gt;=0,"0%–25%",IF(Q30&gt;=-0.25,"0%～−25%",IF(Q30&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ30" s="4" t="inlineStr">
+        <is>
+          <t>小於 −50%</t>
+        </is>
       </c>
       <c r="AK30" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 guc/dist/20261025_創意模型_v0.1.xlsx Val!B42；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 guc/dist/20261025_創意模型_v0.1.1.xlsx Val!B42；投資建議 guc/dist/20261025_創意模型_v0.1.1.xlsx Val!B135；級距 guc/dist/20261025_創意模型_v0.1.1.xlsx Val!B134</t>
         </is>
       </c>
     </row>
@@ -11779,19 +11792,19 @@
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>322.275820410306</v>
+        <v>322.534682310793</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>cohr/dist/20261025_Coherent模型_v0.2.xlsx Val!B39</t>
+          <t>cohr/dist/20261026_Coherent模型_v0.2.2.xlsx Val!B39</t>
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>126.539219389886</v>
+        <v>126.00352198982</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>cohr/dist/20261025_Coherent模型_v0.2.xlsx Val!D23</t>
+          <t>cohr/dist/20261026_Coherent模型_v0.2.2.xlsx Val!D23</t>
         </is>
       </c>
       <c r="N33">
@@ -11807,18 +11820,19 @@
         <v/>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>0.540736340824717</v>
+        <v>0.54197390787777</v>
       </c>
       <c r="R33">
         <f>P33/N33-1</f>
         <v/>
       </c>
-      <c r="S33">
-        <f>IF(Q33&gt;0.5,"強力買進",IF(Q33&gt;0.25,"買進",IF(Q33&gt;=-0.25,"中立",IF(Q33&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S33" s="4" t="inlineStr">
+        <is>
+          <t>強力買進</t>
+        </is>
       </c>
       <c r="T33">
-        <f>319.789455314265/N33-1</f>
+        <f>319.571046584482/N33-1</f>
         <v/>
       </c>
       <c r="U33" t="inlineStr">
@@ -11828,12 +11842,12 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>14.3 ／ 15.5 ／ 17.0</t>
+          <t>14.4 ／ 15.5 ／ 17.0</t>
         </is>
       </c>
       <c r="W33" s="1" t="inlineStr">
         <is>
-          <t>DCF 目標價 206.3（Val!B24）；Comparable 目標價 438.2（Val!B40）；市場共識目標價 394.8（Val!B41，外部、僅供對照）；價格帶 C～A 情境 DCF 126.5～272.6</t>
+          <t>DCF 目標價 207.0（Val!B24）；Comparable 目標價 438.0（Val!B40）；市場共識目標價 394.8（Val!B41，外部、僅供對照）；價格帶 C～A 情境 DCF 126.0～275.4</t>
         </is>
       </c>
       <c r="Z33">
@@ -11856,18 +11870,18 @@
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>16 個情境年度淨利（不含實績），全部為正</t>
+          <t>18 個情境年度淨利（不含實績），全部為正</t>
         </is>
       </c>
       <c r="AE33" s="4" t="n">
-        <v>51.46480793420181</v>
+        <v>55.73323142808181</v>
       </c>
       <c r="AF33" s="4" t="n">
-        <v>2.07656731774848</v>
+        <v>2.06947608283373</v>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>[Derived] cohr/dist/20261025_Coherent模型_v0.2.xlsx PL!E13…PL!J39</t>
+          <t>[Derived] cohr/dist/20261026_Coherent模型_v0.2.2.xlsx PL!E13…PL!J39</t>
         </is>
       </c>
       <c r="AH33">
@@ -11878,13 +11892,14 @@
         <f>IF(S33="未上市","未上市",IF(AND(AH33="不通過",OR(S33="強力買進",S33="買進",S33="未估值")),"收支不足",S33))</f>
         <v/>
       </c>
-      <c r="AJ33">
-        <f>IF(Q33&gt;0.5,"大於 50%",IF(Q33&gt;0.25,"25%–50%",IF(Q33&gt;=0,"0%–25%",IF(Q33&gt;=-0.25,"0%～−25%",IF(Q33&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ33" s="4" t="inlineStr">
+        <is>
+          <t>大於 50%</t>
+        </is>
       </c>
       <c r="AK33" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 cohr/dist/20261025_Coherent模型_v0.2.xlsx Val!B42；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 cohr/dist/20261026_Coherent模型_v0.2.2.xlsx Val!B42；投資建議 cohr/dist/20261026_Coherent模型_v0.2.2.xlsx Val!B50；級距 cohr/dist/20261026_Coherent模型_v0.2.2.xlsx Val!B49</t>
         </is>
       </c>
     </row>
@@ -11914,19 +11929,19 @@
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>611.903536008153</v>
+        <v>623.399886042049</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>lite/dist/20261025_Lumentum模型_v0.2.xlsx Val!B39</t>
+          <t>lite/dist/20261026_Lumentum模型_v0.2.2.xlsx Val!B39</t>
         </is>
       </c>
       <c r="J34" s="4" t="n">
-        <v>216.979769703727</v>
+        <v>211.148558750336</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>lite/dist/20261025_Lumentum模型_v0.2.xlsx Val!D23</t>
+          <t>lite/dist/20261026_Lumentum模型_v0.2.2.xlsx Val!D23</t>
         </is>
       </c>
       <c r="N34">
@@ -11942,18 +11957,19 @@
         <v/>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.190785754515317</v>
+        <v>-0.175582361053666</v>
       </c>
       <c r="R34">
         <f>P34/N34-1</f>
         <v/>
       </c>
-      <c r="S34">
-        <f>IF(Q34&gt;0.5,"強力買進",IF(Q34&gt;0.25,"買進",IF(Q34&gt;=-0.25,"中立",IF(Q34&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S34" s="4" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
       </c>
       <c r="T34">
-        <f>409.473484390874/N34-1</f>
+        <f>410.587041312467/N34-1</f>
         <v/>
       </c>
       <c r="U34" t="inlineStr">
@@ -11963,12 +11979,12 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>24.1 ／ 26.6 ／ 29.7</t>
+          <t>23.1 ／ 26.6 ／ 30.2</t>
         </is>
       </c>
       <c r="W34" s="1" t="inlineStr">
         <is>
-          <t>DCF 目標價 375.8（Val!B24）；Comparable 目標價 848.1（Val!B40）；市場共識目標價 1,165.0（Val!B41，外部、僅供對照）；價格帶 C～A 情境 DCF 217.0～508.3</t>
+          <t>DCF 目標價 387.1（Val!B24）；Comparable 目標價 859.7（Val!B40）；市場共識目標價 1,165.0（Val!B41，外部、僅供對照）；價格帶 C～A 情境 DCF 211.1～549.9</t>
         </is>
       </c>
       <c r="Z34">
@@ -11991,18 +12007,18 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>16 個情境年度淨利（不含實績），全部為正</t>
+          <t>18 個情境年度淨利（不含實績），全部為正</t>
         </is>
       </c>
       <c r="AE34" s="4" t="n">
-        <v>48.07362009652756</v>
+        <v>54.05090141367878</v>
       </c>
       <c r="AF34" s="4" t="n">
-        <v>1.70727274119044</v>
+        <v>1.65482793612448</v>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>[Derived] lite/dist/20261025_Lumentum模型_v0.2.xlsx PL!E13…PL!J39</t>
+          <t>[Derived] lite/dist/20261026_Lumentum模型_v0.2.2.xlsx PL!E13…PL!J39</t>
         </is>
       </c>
       <c r="AH34">
@@ -12013,13 +12029,14 @@
         <f>IF(S34="未上市","未上市",IF(AND(AH34="不通過",OR(S34="強力買進",S34="買進",S34="未估值")),"收支不足",S34))</f>
         <v/>
       </c>
-      <c r="AJ34">
-        <f>IF(Q34&gt;0.5,"大於 50%",IF(Q34&gt;0.25,"25%–50%",IF(Q34&gt;=0,"0%–25%",IF(Q34&gt;=-0.25,"0%～−25%",IF(Q34&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ34" s="4" t="inlineStr">
+        <is>
+          <t>0%～−25%</t>
+        </is>
       </c>
       <c r="AK34" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 lite/dist/20261025_Lumentum模型_v0.2.xlsx Val!B42；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 lite/dist/20261026_Lumentum模型_v0.2.2.xlsx Val!B42；投資建議 lite/dist/20261026_Lumentum模型_v0.2.2.xlsx Val!B50；級距 lite/dist/20261026_Lumentum模型_v0.2.2.xlsx Val!B49</t>
         </is>
       </c>
     </row>
@@ -12049,19 +12066,19 @@
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>797.810166290206</v>
+        <v>791.558609426747</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>eoptolink/dist/20261025_新易盛模型_v0.2.xlsx Val!B39</t>
+          <t>eoptolink/dist/20261026_新易盛模型_v0.2.2.xlsx Val!B39</t>
         </is>
       </c>
       <c r="J35" s="4" t="n">
-        <v>304.979041887906</v>
+        <v>307.265758949729</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>eoptolink/dist/20261025_新易盛模型_v0.2.xlsx Val!D23</t>
+          <t>eoptolink/dist/20261026_新易盛模型_v0.2.2.xlsx Val!D23</t>
         </is>
       </c>
       <c r="N35">
@@ -12077,18 +12094,19 @@
         <v/>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>2.05674393214638</v>
+        <v>2.03279160699903</v>
       </c>
       <c r="R35">
         <f>P35/N35-1</f>
         <v/>
       </c>
-      <c r="S35">
-        <f>IF(Q35&gt;0.5,"強力買進",IF(Q35&gt;0.25,"買進",IF(Q35&gt;=-0.25,"中立",IF(Q35&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S35" s="4" t="inlineStr">
+        <is>
+          <t>強力買進</t>
+        </is>
       </c>
       <c r="T35">
-        <f>1150.67817266164/N35-1</f>
+        <f>1146.39392147938/N35-1</f>
         <v/>
       </c>
       <c r="U35" t="inlineStr">
@@ -12098,12 +12116,12 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>9.0 ／ 11.4 ／ 15.6</t>
+          <t>9.3 ／ 11.4 ／ 15.4</t>
         </is>
       </c>
       <c r="W35" s="1" t="inlineStr">
         <is>
-          <t>DCF 目標價 516.2（Val!B24）；Comparable 目標價 1,079.4（Val!B40）；市場共識目標價 460.9（Val!B41，外部、僅供對照）；價格帶 C～A 情境 DCF 305.0～652.7</t>
+          <t>DCF 目標價 512.7（Val!B24）；Comparable 目標價 1,070.4（Val!B40）；市場共識目標價 460.9（Val!B41，外部、僅供對照）；價格帶 C～A 情境 DCF 307.3～639.5</t>
         </is>
       </c>
       <c r="Z35">
@@ -12126,18 +12144,18 @@
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>17 個情境年度淨利（不含實績），全部為正</t>
+          <t>19 個情境年度淨利（不含實績），全部為正</t>
         </is>
       </c>
       <c r="AE35" s="4" t="n">
-        <v>721.2419002987186</v>
+        <v>788.309493718513</v>
       </c>
       <c r="AF35" s="4" t="n">
         <v>20.0605180178692</v>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>[Derived] eoptolink/dist/20261025_新易盛模型_v0.2.xlsx PL!D12…PL!J36</t>
+          <t>[Derived] eoptolink/dist/20261026_新易盛模型_v0.2.2.xlsx PL!D12…PL!J36</t>
         </is>
       </c>
       <c r="AH35">
@@ -12148,13 +12166,14 @@
         <f>IF(S35="未上市","未上市",IF(AND(AH35="不通過",OR(S35="強力買進",S35="買進",S35="未估值")),"收支不足",S35))</f>
         <v/>
       </c>
-      <c r="AJ35">
-        <f>IF(Q35&gt;0.5,"大於 50%",IF(Q35&gt;0.25,"25%–50%",IF(Q35&gt;=0,"0%–25%",IF(Q35&gt;=-0.25,"0%～−25%",IF(Q35&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ35" s="4" t="inlineStr">
+        <is>
+          <t>大於 50%</t>
+        </is>
       </c>
       <c r="AK35" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 eoptolink/dist/20261025_新易盛模型_v0.2.xlsx Val!B42；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 eoptolink/dist/20261026_新易盛模型_v0.2.2.xlsx Val!B42；投資建議 eoptolink/dist/20261026_新易盛模型_v0.2.2.xlsx Val!B50；級距 eoptolink/dist/20261026_新易盛模型_v0.2.2.xlsx Val!B49</t>
         </is>
       </c>
     </row>
@@ -12188,7 +12207,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>accton/dist/20261025_智邦模型_v0.2.xlsx Val!B39</t>
+          <t>accton/dist/20261025_智邦模型_v0.2.1.xlsx Val!B39</t>
         </is>
       </c>
       <c r="J36" s="4" t="n">
@@ -12196,7 +12215,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>accton/dist/20261025_智邦模型_v0.2.xlsx Val!B46</t>
+          <t>accton/dist/20261025_智邦模型_v0.2.1.xlsx Val!B46</t>
         </is>
       </c>
       <c r="N36">
@@ -12218,9 +12237,10 @@
         <f>P36/N36-1</f>
         <v/>
       </c>
-      <c r="S36">
-        <f>IF(Q36&gt;0.5,"強力買進",IF(Q36&gt;0.25,"買進",IF(Q36&gt;=-0.25,"中立",IF(Q36&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S36" s="4" t="inlineStr">
+        <is>
+          <t>買進</t>
+        </is>
       </c>
       <c r="T36">
         <f>3452.51414467191/N36-1</f>
@@ -12272,7 +12292,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>[Derived] accton/dist/20261025_智邦模型_v0.2.xlsx PL!D13…PL!G39</t>
+          <t>[Derived] accton/dist/20261025_智邦模型_v0.2.1.xlsx PL!D13…PL!G39</t>
         </is>
       </c>
       <c r="AH36">
@@ -12283,13 +12303,14 @@
         <f>IF(S36="未上市","未上市",IF(AND(AH36="不通過",OR(S36="強力買進",S36="買進",S36="未估值")),"收支不足",S36))</f>
         <v/>
       </c>
-      <c r="AJ36">
-        <f>IF(Q36&gt;0.5,"大於 50%",IF(Q36&gt;0.25,"25%–50%",IF(Q36&gt;=0,"0%–25%",IF(Q36&gt;=-0.25,"0%～−25%",IF(Q36&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ36" s="4" t="inlineStr">
+        <is>
+          <t>25%–50%</t>
+        </is>
       </c>
       <c r="AK36" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 accton/dist/20261025_智邦模型_v0.2.xlsx Val!B42；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 accton/dist/20261025_智邦模型_v0.2.1.xlsx Val!B42；投資建議 accton/dist/20261025_智邦模型_v0.2.1.xlsx Val!B52；級距 accton/dist/20261025_智邦模型_v0.2.1.xlsx Val!B51</t>
         </is>
       </c>
     </row>
@@ -12319,19 +12340,19 @@
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>360.601895050031</v>
+        <v>373.123198537049</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>fabrinet/dist/20261025_Fabrinet模型_v0.1.xlsx Val!B39</t>
+          <t>fabrinet/dist/20261026_Fabrinet模型_v0.1.2.xlsx Val!B39</t>
         </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v>164.552284506867</v>
+        <v>163.840959069597</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fabrinet/dist/20261025_Fabrinet模型_v0.1.xlsx Val!D23</t>
+          <t>fabrinet/dist/20261026_Fabrinet模型_v0.1.2.xlsx Val!D23</t>
         </is>
       </c>
       <c r="N37">
@@ -12347,18 +12368,19 @@
         <v/>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>0.144986013367724</v>
+        <v>0.184743756071152</v>
       </c>
       <c r="R37">
         <f>P37/N37-1</f>
         <v/>
       </c>
-      <c r="S37">
-        <f>IF(Q37&gt;0.5,"強力買進",IF(Q37&gt;0.25,"買進",IF(Q37&gt;=-0.25,"中立",IF(Q37&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S37" s="4" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
       </c>
       <c r="T37">
-        <f>406.817486657285/N37-1</f>
+        <f>408.001544364806/N37-1</f>
         <v/>
       </c>
       <c r="U37" t="inlineStr">
@@ -12368,12 +12390,12 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>11.7 ／ 14.3 ／ 18.1</t>
+          <t>11.3 ／ 14.3 ／ 18.0</t>
         </is>
       </c>
       <c r="W37" s="1" t="inlineStr">
         <is>
-          <t>DCF 目標價 332.2（Val!B24）；Comparable 目標價 389.0（Val!B40）；市場共識目標價 687.8（Val!B41，外部、僅供對照）；價格帶 C～A 情境 DCF 164.6～505.0</t>
+          <t>DCF 目標價 349.8（Val!B24）；Comparable 目標價 396.5（Val!B40）；市場共識目標價 687.8（Val!B41，外部、僅供對照）；價格帶 C～A 情境 DCF 163.8～564.3</t>
         </is>
       </c>
       <c r="Z37">
@@ -12400,14 +12422,14 @@
         </is>
       </c>
       <c r="AE37" s="4" t="n">
-        <v>15.77740453289506</v>
+        <v>16.45838145404598</v>
       </c>
       <c r="AF37" s="4" t="n">
-        <v>0.452041842422224</v>
+        <v>0.449392515917191</v>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>[Derived] fabrinet/dist/20261025_Fabrinet模型_v0.1.xlsx PL!E15…PL!J45</t>
+          <t>[Derived] fabrinet/dist/20261026_Fabrinet模型_v0.1.2.xlsx PL!E15…PL!J45</t>
         </is>
       </c>
       <c r="AH37">
@@ -12418,13 +12440,14 @@
         <f>IF(S37="未上市","未上市",IF(AND(AH37="不通過",OR(S37="強力買進",S37="買進",S37="未估值")),"收支不足",S37))</f>
         <v/>
       </c>
-      <c r="AJ37">
-        <f>IF(Q37&gt;0.5,"大於 50%",IF(Q37&gt;0.25,"25%–50%",IF(Q37&gt;=0,"0%–25%",IF(Q37&gt;=-0.25,"0%～−25%",IF(Q37&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ37" s="4" t="inlineStr">
+        <is>
+          <t>0%–25%</t>
+        </is>
       </c>
       <c r="AK37" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 fabrinet/dist/20261025_Fabrinet模型_v0.1.xlsx Val!B42；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 fabrinet/dist/20261026_Fabrinet模型_v0.1.2.xlsx Val!B42；投資建議 fabrinet/dist/20261026_Fabrinet模型_v0.1.2.xlsx Val!B50；級距 fabrinet/dist/20261026_Fabrinet模型_v0.1.2.xlsx Val!B49</t>
         </is>
       </c>
     </row>
@@ -12454,19 +12477,19 @@
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>195.696397392632</v>
+        <v>194.503855731343</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>crdo/dist/20261025_Credo模型_v0.2.xlsx Val!B39</t>
+          <t>crdo/dist/20261026_Credo模型_v0.2.2.xlsx Val!B39</t>
         </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v>53.1251226501538</v>
+        <v>53.662353127775</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>crdo/dist/20261025_Credo模型_v0.2.xlsx Val!D23</t>
+          <t>crdo/dist/20261026_Credo模型_v0.2.2.xlsx Val!D23</t>
         </is>
       </c>
       <c r="N38">
@@ -12482,18 +12505,19 @@
         <v/>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>0.328646869391217</v>
+        <v>0.320550313879711</v>
       </c>
       <c r="R38">
         <f>P38/N38-1</f>
         <v/>
       </c>
-      <c r="S38">
-        <f>IF(Q38&gt;0.5,"強力買進",IF(Q38&gt;0.25,"買進",IF(Q38&gt;=-0.25,"中立",IF(Q38&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S38" s="4" t="inlineStr">
+        <is>
+          <t>買進</t>
+        </is>
       </c>
       <c r="T38">
-        <f>620.46087778403/N38-1</f>
+        <f>619.6489358636/N38-1</f>
         <v/>
       </c>
       <c r="U38" t="inlineStr">
@@ -12503,12 +12527,12 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>16.0 ／ 17.3 ／ 18.9</t>
+          <t>16.2 ／ 17.3 ／ 18.8</t>
         </is>
       </c>
       <c r="W38" s="1" t="inlineStr">
         <is>
-          <t>DCF 目標價 101.3（Val!B24）；Comparable 目標價 290.1（Val!B40）；市場共識目標價 279.1（Val!B41，外部、僅供對照）；價格帶 C～A 情境 DCF 53.1～143.4</t>
+          <t>DCF 目標價 100.2（Val!B24）；Comparable 目標價 288.8（Val!B40）；市場共識目標價 279.1（Val!B41，外部、僅供對照）；價格帶 C～A 情境 DCF 53.7～139.2</t>
         </is>
       </c>
       <c r="Z38">
@@ -12535,14 +12559,14 @@
         </is>
       </c>
       <c r="AE38" s="4" t="n">
-        <v>26.24478412100936</v>
+        <v>26.00564440421192</v>
       </c>
       <c r="AF38" s="4" t="n">
-        <v>0.791263045056819</v>
+        <v>0.801215260866878</v>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>[Derived] crdo/dist/20261025_Credo模型_v0.2.xlsx PL!E13…PL!J39</t>
+          <t>[Derived] crdo/dist/20261026_Credo模型_v0.2.2.xlsx PL!E13…PL!J39</t>
         </is>
       </c>
       <c r="AH38">
@@ -12553,13 +12577,14 @@
         <f>IF(S38="未上市","未上市",IF(AND(AH38="不通過",OR(S38="強力買進",S38="買進",S38="未估值")),"收支不足",S38))</f>
         <v/>
       </c>
-      <c r="AJ38">
-        <f>IF(Q38&gt;0.5,"大於 50%",IF(Q38&gt;0.25,"25%–50%",IF(Q38&gt;=0,"0%–25%",IF(Q38&gt;=-0.25,"0%～−25%",IF(Q38&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ38" s="4" t="inlineStr">
+        <is>
+          <t>25%–50%</t>
+        </is>
       </c>
       <c r="AK38" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 crdo/dist/20261025_Credo模型_v0.2.xlsx Val!B42；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 crdo/dist/20261026_Credo模型_v0.2.2.xlsx Val!B42；投資建議 crdo/dist/20261026_Credo模型_v0.2.2.xlsx Val!B130；級距 crdo/dist/20261026_Credo模型_v0.2.2.xlsx Val!B129</t>
         </is>
       </c>
     </row>
@@ -12593,7 +12618,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>alab/dist/20261025_Astera Labs模型_v0.1.xlsx Val!B39</t>
+          <t>alab/dist/20261025_Astera Labs模型_v0.1.1.xlsx Val!B39</t>
         </is>
       </c>
       <c r="J39" s="4" t="n">
@@ -12601,7 +12626,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>alab/dist/20261025_Astera Labs模型_v0.1.xlsx Val!D23</t>
+          <t>alab/dist/20261025_Astera Labs模型_v0.1.1.xlsx Val!D23</t>
         </is>
       </c>
       <c r="N39">
@@ -12623,9 +12648,10 @@
         <f>P39/N39-1</f>
         <v/>
       </c>
-      <c r="S39">
-        <f>IF(Q39&gt;0.5,"強力買進",IF(Q39&gt;0.25,"買進",IF(Q39&gt;=-0.25,"中立",IF(Q39&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S39" s="4" t="inlineStr">
+        <is>
+          <t>放空</t>
+        </is>
       </c>
       <c r="T39">
         <f>616.322122932452/N39-1</f>
@@ -12677,7 +12703,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>[Derived] alab/dist/20261025_Astera Labs模型_v0.1.xlsx PL!D12…PL!J36</t>
+          <t>[Derived] alab/dist/20261025_Astera Labs模型_v0.1.1.xlsx PL!D12…PL!J36</t>
         </is>
       </c>
       <c r="AH39">
@@ -12688,13 +12714,14 @@
         <f>IF(S39="未上市","未上市",IF(AND(AH39="不通過",OR(S39="強力買進",S39="買進",S39="未估值")),"收支不足",S39))</f>
         <v/>
       </c>
-      <c r="AJ39">
-        <f>IF(Q39&gt;0.5,"大於 50%",IF(Q39&gt;0.25,"25%–50%",IF(Q39&gt;=0,"0%–25%",IF(Q39&gt;=-0.25,"0%～−25%",IF(Q39&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ39" s="4" t="inlineStr">
+        <is>
+          <t>−25%～−50%</t>
+        </is>
       </c>
       <c r="AK39" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 alab/dist/20261025_Astera Labs模型_v0.1.xlsx Val!B42；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 alab/dist/20261025_Astera Labs模型_v0.1.1.xlsx Val!B42；投資建議 alab/dist/20261025_Astera Labs模型_v0.1.1.xlsx Val!B130；級距 alab/dist/20261025_Astera Labs模型_v0.1.1.xlsx Val!B129</t>
         </is>
       </c>
     </row>
@@ -12728,7 +12755,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>kyec/dist/20261025_京元電模型_v0.2.xlsx Val!B39</t>
+          <t>kyec/dist/20261025_京元電模型_v0.2.1.xlsx Val!B39</t>
         </is>
       </c>
       <c r="J40" s="4" t="n">
@@ -12736,7 +12763,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>kyec/dist/20261025_京元電模型_v0.2.xlsx Val!D23</t>
+          <t>kyec/dist/20261025_京元電模型_v0.2.1.xlsx Val!D23</t>
         </is>
       </c>
       <c r="N40">
@@ -12758,9 +12785,10 @@
         <f>P40/N40-1</f>
         <v/>
       </c>
-      <c r="S40">
-        <f>IF(Q40&gt;0.5,"強力買進",IF(Q40&gt;0.25,"買進",IF(Q40&gt;=-0.25,"中立",IF(Q40&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S40" s="4" t="inlineStr">
+        <is>
+          <t>放空</t>
+        </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -12803,7 +12831,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>[Derived] kyec/dist/20261025_京元電模型_v0.2.xlsx PL!D14…PL!J42</t>
+          <t>[Derived] kyec/dist/20261025_京元電模型_v0.2.1.xlsx PL!D14…PL!J42</t>
         </is>
       </c>
       <c r="AH40">
@@ -12814,13 +12842,14 @@
         <f>IF(S40="未上市","未上市",IF(AND(AH40="不通過",OR(S40="強力買進",S40="買進",S40="未估值")),"收支不足",S40))</f>
         <v/>
       </c>
-      <c r="AJ40">
-        <f>IF(Q40&gt;0.5,"大於 50%",IF(Q40&gt;0.25,"25%–50%",IF(Q40&gt;=0,"0%–25%",IF(Q40&gt;=-0.25,"0%～−25%",IF(Q40&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ40" s="4" t="inlineStr">
+        <is>
+          <t>−25%～−50%</t>
+        </is>
       </c>
       <c r="AK40" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 kyec/dist/20261025_京元電模型_v0.2.xlsx Val!B42；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 kyec/dist/20261025_京元電模型_v0.2.1.xlsx Val!B42；投資建議 kyec/dist/20261025_京元電模型_v0.2.1.xlsx Val!B50；級距 kyec/dist/20261025_京元電模型_v0.2.1.xlsx Val!B49</t>
         </is>
       </c>
     </row>
@@ -12854,7 +12883,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>amkr/dist/20261025_艾克爾模型_v0.2.xlsx Val!B39</t>
+          <t>amkr/dist/20261025_艾克爾模型_v0.2.1.xlsx Val!B39</t>
         </is>
       </c>
       <c r="J41" s="4" t="n">
@@ -12862,7 +12891,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>amkr/dist/20261025_艾克爾模型_v0.2.xlsx Val!D23</t>
+          <t>amkr/dist/20261025_艾克爾模型_v0.2.1.xlsx Val!D23</t>
         </is>
       </c>
       <c r="N41">
@@ -12884,9 +12913,10 @@
         <f>P41/N41-1</f>
         <v/>
       </c>
-      <c r="S41">
-        <f>IF(Q41&gt;0.5,"強力買進",IF(Q41&gt;0.25,"買進",IF(Q41&gt;=-0.25,"中立",IF(Q41&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S41" s="4" t="inlineStr">
+        <is>
+          <t>買進</t>
+        </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -12929,7 +12959,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>[Derived] amkr/dist/20261025_艾克爾模型_v0.2.xlsx PL!D14…PL!J44</t>
+          <t>[Derived] amkr/dist/20261025_艾克爾模型_v0.2.1.xlsx PL!D14…PL!J44</t>
         </is>
       </c>
       <c r="AH41">
@@ -12940,13 +12970,14 @@
         <f>IF(S41="未上市","未上市",IF(AND(AH41="不通過",OR(S41="強力買進",S41="買進",S41="未估值")),"收支不足",S41))</f>
         <v/>
       </c>
-      <c r="AJ41">
-        <f>IF(Q41&gt;0.5,"大於 50%",IF(Q41&gt;0.25,"25%–50%",IF(Q41&gt;=0,"0%–25%",IF(Q41&gt;=-0.25,"0%～−25%",IF(Q41&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ41" s="4" t="inlineStr">
+        <is>
+          <t>25%–50%</t>
+        </is>
       </c>
       <c r="AK41" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 amkr/dist/20261025_艾克爾模型_v0.2.xlsx Val!B42；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 amkr/dist/20261025_艾克爾模型_v0.2.1.xlsx Val!B42；投資建議 amkr/dist/20261025_艾克爾模型_v0.2.1.xlsx Val!B50；級距 amkr/dist/20261025_艾克爾模型_v0.2.1.xlsx Val!B49</t>
         </is>
       </c>
     </row>
@@ -12980,7 +13011,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>emc/dist/20261025_台光電模型_v0.2.xlsx Val!B118</t>
+          <t>emc/dist/20261025_台光電模型_v0.2.1.xlsx Val!B118</t>
         </is>
       </c>
       <c r="J42" s="4" t="n">
@@ -12988,7 +13019,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>emc/dist/20261025_台光電模型_v0.2.xlsx Val!D104</t>
+          <t>emc/dist/20261025_台光電模型_v0.2.1.xlsx Val!D104</t>
         </is>
       </c>
       <c r="N42">
@@ -13010,9 +13041,10 @@
         <f>P42/N42-1</f>
         <v/>
       </c>
-      <c r="S42">
-        <f>IF(Q42&gt;0.5,"強力買進",IF(Q42&gt;0.25,"買進",IF(Q42&gt;=-0.25,"中立",IF(Q42&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S42" s="4" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
       </c>
       <c r="T42">
         <f>2904.876796827/N42-1</f>
@@ -13064,7 +13096,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>[Derived] emc/dist/20261025_台光電模型_v0.2.xlsx PL!D12…PL!G36</t>
+          <t>[Derived] emc/dist/20261025_台光電模型_v0.2.1.xlsx PL!D12…PL!G36</t>
         </is>
       </c>
       <c r="AH42">
@@ -13075,13 +13107,14 @@
         <f>IF(S42="未上市","未上市",IF(AND(AH42="不通過",OR(S42="強力買進",S42="買進",S42="未估值")),"收支不足",S42))</f>
         <v/>
       </c>
-      <c r="AJ42">
-        <f>IF(Q42&gt;0.5,"大於 50%",IF(Q42&gt;0.25,"25%–50%",IF(Q42&gt;=0,"0%–25%",IF(Q42&gt;=-0.25,"0%～−25%",IF(Q42&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ42" s="4" t="inlineStr">
+        <is>
+          <t>0%–25%</t>
+        </is>
       </c>
       <c r="AK42" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 emc/dist/20261025_台光電模型_v0.2.xlsx Val!B121；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 emc/dist/20261025_台光電模型_v0.2.1.xlsx Val!B121；投資建議 emc/dist/20261025_台光電模型_v0.2.1.xlsx Val!B132；級距 emc/dist/20261025_台光電模型_v0.2.1.xlsx Val!B131</t>
         </is>
       </c>
     </row>
@@ -13115,7 +13148,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>unimicron/dist/20261025_欣興模型_v0.1.xlsx Val!B39</t>
+          <t>unimicron/dist/20261025_欣興模型_v0.1.1.xlsx Val!B39</t>
         </is>
       </c>
       <c r="J43" s="4" t="n">
@@ -13123,7 +13156,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>unimicron/dist/20261025_欣興模型_v0.1.xlsx Val!D23</t>
+          <t>unimicron/dist/20261025_欣興模型_v0.1.1.xlsx Val!D23</t>
         </is>
       </c>
       <c r="N43">
@@ -13145,9 +13178,10 @@
         <f>P43/N43-1</f>
         <v/>
       </c>
-      <c r="S43">
-        <f>IF(Q43&gt;0.5,"強力買進",IF(Q43&gt;0.25,"買進",IF(Q43&gt;=-0.25,"中立",IF(Q43&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S43" s="4" t="inlineStr">
+        <is>
+          <t>放空</t>
+        </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -13190,7 +13224,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>[Derived] unimicron/dist/20261025_欣興模型_v0.1.xlsx PL!D13…PL!J41</t>
+          <t>[Derived] unimicron/dist/20261025_欣興模型_v0.1.1.xlsx PL!D13…PL!J41</t>
         </is>
       </c>
       <c r="AH43">
@@ -13201,13 +13235,14 @@
         <f>IF(S43="未上市","未上市",IF(AND(AH43="不通過",OR(S43="強力買進",S43="買進",S43="未估值")),"收支不足",S43))</f>
         <v/>
       </c>
-      <c r="AJ43">
-        <f>IF(Q43&gt;0.5,"大於 50%",IF(Q43&gt;0.25,"25%–50%",IF(Q43&gt;=0,"0%–25%",IF(Q43&gt;=-0.25,"0%～−25%",IF(Q43&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ43" s="4" t="inlineStr">
+        <is>
+          <t>−25%～−50%</t>
+        </is>
       </c>
       <c r="AK43" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 unimicron/dist/20261025_欣興模型_v0.1.xlsx Val!B42；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 unimicron/dist/20261025_欣興模型_v0.1.1.xlsx Val!B42；投資建議 unimicron/dist/20261025_欣興模型_v0.1.1.xlsx Val!B134；級距 unimicron/dist/20261025_欣興模型_v0.1.1.xlsx Val!B133</t>
         </is>
       </c>
     </row>
@@ -13241,7 +13276,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>nanya_pcb/dist/20261025_南電模型_v0.1.xlsx Val!B39</t>
+          <t>nanya_pcb/dist/20261025_南電模型_v0.1.1.xlsx Val!B39</t>
         </is>
       </c>
       <c r="J44" s="4" t="n">
@@ -13249,7 +13284,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>nanya_pcb/dist/20261025_南電模型_v0.1.xlsx Val!D23</t>
+          <t>nanya_pcb/dist/20261025_南電模型_v0.1.1.xlsx Val!D23</t>
         </is>
       </c>
       <c r="N44">
@@ -13271,9 +13306,10 @@
         <f>P44/N44-1</f>
         <v/>
       </c>
-      <c r="S44">
-        <f>IF(Q44&gt;0.5,"強力買進",IF(Q44&gt;0.25,"買進",IF(Q44&gt;=-0.25,"中立",IF(Q44&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S44" s="4" t="inlineStr">
+        <is>
+          <t>放空</t>
+        </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -13316,7 +13352,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>[Derived] nanya_pcb/dist/20261025_南電模型_v0.1.xlsx PL!D13…PL!J41</t>
+          <t>[Derived] nanya_pcb/dist/20261025_南電模型_v0.1.1.xlsx PL!D13…PL!J41</t>
         </is>
       </c>
       <c r="AH44">
@@ -13327,13 +13363,14 @@
         <f>IF(S44="未上市","未上市",IF(AND(AH44="不通過",OR(S44="強力買進",S44="買進",S44="未估值")),"收支不足",S44))</f>
         <v/>
       </c>
-      <c r="AJ44">
-        <f>IF(Q44&gt;0.5,"大於 50%",IF(Q44&gt;0.25,"25%–50%",IF(Q44&gt;=0,"0%–25%",IF(Q44&gt;=-0.25,"0%～−25%",IF(Q44&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ44" s="4" t="inlineStr">
+        <is>
+          <t>−25%～−50%</t>
+        </is>
       </c>
       <c r="AK44" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 nanya_pcb/dist/20261025_南電模型_v0.1.xlsx Val!B42；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 nanya_pcb/dist/20261025_南電模型_v0.1.1.xlsx Val!B42；投資建議 nanya_pcb/dist/20261025_南電模型_v0.1.1.xlsx Val!B134；級距 nanya_pcb/dist/20261025_南電模型_v0.1.1.xlsx Val!B133</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13404,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>gce/dist/20261025_金像電模型_v0.1.xlsx Val!B40</t>
+          <t>gce/dist/20261025_金像電模型_v0.1.1.xlsx Val!B40</t>
         </is>
       </c>
       <c r="J45" s="4" t="n">
@@ -13375,7 +13412,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>gce/dist/20261025_金像電模型_v0.1.xlsx Val!D23</t>
+          <t>gce/dist/20261025_金像電模型_v0.1.1.xlsx Val!D23</t>
         </is>
       </c>
       <c r="N45">
@@ -13397,9 +13434,10 @@
         <f>P45/N45-1</f>
         <v/>
       </c>
-      <c r="S45">
-        <f>IF(Q45&gt;0.5,"強力買進",IF(Q45&gt;0.25,"買進",IF(Q45&gt;=-0.25,"中立",IF(Q45&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S45" s="4" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -13442,7 +13480,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>[Derived] gce/dist/20261025_金像電模型_v0.1.xlsx PL!D12…PL!J38</t>
+          <t>[Derived] gce/dist/20261025_金像電模型_v0.1.1.xlsx PL!D12…PL!J38</t>
         </is>
       </c>
       <c r="AH45">
@@ -13453,13 +13491,14 @@
         <f>IF(S45="未上市","未上市",IF(AND(AH45="不通過",OR(S45="強力買進",S45="買進",S45="未估值")),"收支不足",S45))</f>
         <v/>
       </c>
-      <c r="AJ45">
-        <f>IF(Q45&gt;0.5,"大於 50%",IF(Q45&gt;0.25,"25%–50%",IF(Q45&gt;=0,"0%–25%",IF(Q45&gt;=-0.25,"0%～−25%",IF(Q45&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ45" s="4" t="inlineStr">
+        <is>
+          <t>0%–25%</t>
+        </is>
       </c>
       <c r="AK45" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 gce/dist/20261025_金像電模型_v0.1.xlsx Val!B43；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 gce/dist/20261025_金像電模型_v0.1.1.xlsx Val!B43；投資建議 gce/dist/20261025_金像電模型_v0.1.1.xlsx Val!B119；級距 gce/dist/20261025_金像電模型_v0.1.1.xlsx Val!B118</t>
         </is>
       </c>
     </row>
@@ -13493,7 +13532,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>victory_giant/dist/20261025_勝宏科技模型_v0.1.xlsx Val!B39</t>
+          <t>victory_giant/dist/20261025_勝宏科技模型_v0.1.1.xlsx Val!B39</t>
         </is>
       </c>
       <c r="J46" s="4" t="n">
@@ -13501,7 +13540,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>victory_giant/dist/20261025_勝宏科技模型_v0.1.xlsx Val!D23</t>
+          <t>victory_giant/dist/20261025_勝宏科技模型_v0.1.1.xlsx Val!D23</t>
         </is>
       </c>
       <c r="N46">
@@ -13523,9 +13562,10 @@
         <f>P46/N46-1</f>
         <v/>
       </c>
-      <c r="S46">
-        <f>IF(Q46&gt;0.5,"強力買進",IF(Q46&gt;0.25,"買進",IF(Q46&gt;=-0.25,"中立",IF(Q46&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S46" s="4" t="inlineStr">
+        <is>
+          <t>強力買進</t>
+        </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -13568,7 +13608,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>[Derived] victory_giant/dist/20261025_勝宏科技模型_v0.1.xlsx PL!D12…PL!J38</t>
+          <t>[Derived] victory_giant/dist/20261025_勝宏科技模型_v0.1.1.xlsx PL!D12…PL!J38</t>
         </is>
       </c>
       <c r="AH46">
@@ -13579,13 +13619,14 @@
         <f>IF(S46="未上市","未上市",IF(AND(AH46="不通過",OR(S46="強力買進",S46="買進",S46="未估值")),"收支不足",S46))</f>
         <v/>
       </c>
-      <c r="AJ46">
-        <f>IF(Q46&gt;0.5,"大於 50%",IF(Q46&gt;0.25,"25%–50%",IF(Q46&gt;=0,"0%–25%",IF(Q46&gt;=-0.25,"0%～−25%",IF(Q46&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ46" s="4" t="inlineStr">
+        <is>
+          <t>大於 50%</t>
+        </is>
       </c>
       <c r="AK46" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 victory_giant/dist/20261025_勝宏科技模型_v0.1.xlsx Val!B42；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 victory_giant/dist/20261025_勝宏科技模型_v0.1.1.xlsx Val!B42；投資建議 victory_giant/dist/20261025_勝宏科技模型_v0.1.1.xlsx Val!B119；級距 victory_giant/dist/20261025_勝宏科技模型_v0.1.1.xlsx Val!B118</t>
         </is>
       </c>
     </row>
@@ -13619,7 +13660,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>asml/dist/20261025_ASML模型_v0.2.xlsx Val!B115</t>
+          <t>asml/dist/20261025_ASML模型_v0.2.1.xlsx Val!B115</t>
         </is>
       </c>
       <c r="J47" s="4" t="n">
@@ -13627,7 +13668,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>asml/dist/20261025_ASML模型_v0.2.xlsx Val!D99</t>
+          <t>asml/dist/20261025_ASML模型_v0.2.1.xlsx Val!D99</t>
         </is>
       </c>
       <c r="N47">
@@ -13649,9 +13690,10 @@
         <f>P47/N47-1</f>
         <v/>
       </c>
-      <c r="S47">
-        <f>IF(Q47&gt;0.5,"強力買進",IF(Q47&gt;0.25,"買進",IF(Q47&gt;=-0.25,"中立",IF(Q47&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S47" s="4" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
       </c>
       <c r="T47">
         <f>1829.12787571104/N47-1</f>
@@ -13703,7 +13745,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>[Derived] asml/dist/20261025_ASML模型_v0.2.xlsx PL!D12…PL!G34</t>
+          <t>[Derived] asml/dist/20261025_ASML模型_v0.2.1.xlsx PL!D12…PL!G34</t>
         </is>
       </c>
       <c r="AH47">
@@ -13714,13 +13756,14 @@
         <f>IF(S47="未上市","未上市",IF(AND(AH47="不通過",OR(S47="強力買進",S47="買進",S47="未估值")),"收支不足",S47))</f>
         <v/>
       </c>
-      <c r="AJ47">
-        <f>IF(Q47&gt;0.5,"大於 50%",IF(Q47&gt;0.25,"25%–50%",IF(Q47&gt;=0,"0%–25%",IF(Q47&gt;=-0.25,"0%～−25%",IF(Q47&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ47" s="4" t="inlineStr">
+        <is>
+          <t>0%～−25%</t>
+        </is>
       </c>
       <c r="AK47" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 asml/dist/20261025_ASML模型_v0.2.xlsx Val!B118；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 asml/dist/20261025_ASML模型_v0.2.1.xlsx Val!B118；投資建議 asml/dist/20261025_ASML模型_v0.2.1.xlsx Val!B126；級距 asml/dist/20261025_ASML模型_v0.2.1.xlsx Val!B125</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13797,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>amat/dist/20261025_應用材料模型_v0.2.xlsx Val!B136</t>
+          <t>amat/dist/20261025_應用材料模型_v0.2.1.xlsx Val!B136</t>
         </is>
       </c>
       <c r="J48" s="4" t="n">
@@ -13762,7 +13805,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>amat/dist/20261025_應用材料模型_v0.2.xlsx Val!D121</t>
+          <t>amat/dist/20261025_應用材料模型_v0.2.1.xlsx Val!D121</t>
         </is>
       </c>
       <c r="N48">
@@ -13784,9 +13827,10 @@
         <f>P48/N48-1</f>
         <v/>
       </c>
-      <c r="S48">
-        <f>IF(Q48&gt;0.5,"強力買進",IF(Q48&gt;0.25,"買進",IF(Q48&gt;=-0.25,"中立",IF(Q48&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S48" s="4" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
       </c>
       <c r="T48">
         <f>309.834449680392/N48-1</f>
@@ -13838,7 +13882,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>[Derived] amat/dist/20261025_應用材料模型_v0.2.xlsx PL!D11…PL!G31</t>
+          <t>[Derived] amat/dist/20261025_應用材料模型_v0.2.1.xlsx PL!D11…PL!G31</t>
         </is>
       </c>
       <c r="AH48">
@@ -13849,13 +13893,14 @@
         <f>IF(S48="未上市","未上市",IF(AND(AH48="不通過",OR(S48="強力買進",S48="買進",S48="未估值")),"收支不足",S48))</f>
         <v/>
       </c>
-      <c r="AJ48">
-        <f>IF(Q48&gt;0.5,"大於 50%",IF(Q48&gt;0.25,"25%–50%",IF(Q48&gt;=0,"0%–25%",IF(Q48&gt;=-0.25,"0%～−25%",IF(Q48&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ48" s="4" t="inlineStr">
+        <is>
+          <t>0%～−25%</t>
+        </is>
       </c>
       <c r="AK48" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 amat/dist/20261025_應用材料模型_v0.2.xlsx Val!B139；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 amat/dist/20261025_應用材料模型_v0.2.1.xlsx Val!B139；投資建議 amat/dist/20261025_應用材料模型_v0.2.1.xlsx Val!B147；級距 amat/dist/20261025_應用材料模型_v0.2.1.xlsx Val!B146</t>
         </is>
       </c>
     </row>
@@ -13889,7 +13934,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>lrcx/dist/20261025_科林研發模型_v0.2.xlsx Val!B128</t>
+          <t>lrcx/dist/20261025_科林研發模型_v0.2.1.xlsx Val!B128</t>
         </is>
       </c>
       <c r="J49" s="4" t="n">
@@ -13897,7 +13942,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>lrcx/dist/20261025_科林研發模型_v0.2.xlsx Val!D113</t>
+          <t>lrcx/dist/20261025_科林研發模型_v0.2.1.xlsx Val!D113</t>
         </is>
       </c>
       <c r="N49">
@@ -13919,9 +13964,10 @@
         <f>P49/N49-1</f>
         <v/>
       </c>
-      <c r="S49">
-        <f>IF(Q49&gt;0.5,"強力買進",IF(Q49&gt;0.25,"買進",IF(Q49&gt;=-0.25,"中立",IF(Q49&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S49" s="4" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
       </c>
       <c r="T49">
         <f>154.25592051976/N49-1</f>
@@ -13973,7 +14019,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>[Derived] lrcx/dist/20261025_科林研發模型_v0.2.xlsx PL!E11…PL!G31</t>
+          <t>[Derived] lrcx/dist/20261025_科林研發模型_v0.2.1.xlsx PL!E11…PL!G31</t>
         </is>
       </c>
       <c r="AH49">
@@ -13984,13 +14030,14 @@
         <f>IF(S49="未上市","未上市",IF(AND(AH49="不通過",OR(S49="強力買進",S49="買進",S49="未估值")),"收支不足",S49))</f>
         <v/>
       </c>
-      <c r="AJ49">
-        <f>IF(Q49&gt;0.5,"大於 50%",IF(Q49&gt;0.25,"25%–50%",IF(Q49&gt;=0,"0%–25%",IF(Q49&gt;=-0.25,"0%～−25%",IF(Q49&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ49" s="4" t="inlineStr">
+        <is>
+          <t>0%～−25%</t>
+        </is>
       </c>
       <c r="AK49" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 lrcx/dist/20261025_科林研發模型_v0.2.xlsx Val!B131；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 lrcx/dist/20261025_科林研發模型_v0.2.1.xlsx Val!B131；投資建議 lrcx/dist/20261025_科林研發模型_v0.2.1.xlsx Val!B139；級距 lrcx/dist/20261025_科林研發模型_v0.2.1.xlsx Val!B138</t>
         </is>
       </c>
     </row>
@@ -14024,7 +14071,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>klac/dist/20261025_科磊模型_v0.2.xlsx Val!B129</t>
+          <t>klac/dist/20261025_科磊模型_v0.2.1.xlsx Val!B129</t>
         </is>
       </c>
       <c r="J50" s="4" t="n">
@@ -14032,7 +14079,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>klac/dist/20261025_科磊模型_v0.2.xlsx Val!D113</t>
+          <t>klac/dist/20261025_科磊模型_v0.2.1.xlsx Val!D113</t>
         </is>
       </c>
       <c r="N50">
@@ -14054,9 +14101,10 @@
         <f>P50/N50-1</f>
         <v/>
       </c>
-      <c r="S50">
-        <f>IF(Q50&gt;0.5,"強力買進",IF(Q50&gt;0.25,"買進",IF(Q50&gt;=-0.25,"中立",IF(Q50&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S50" s="4" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
       </c>
       <c r="T50">
         <f>102.08226284068/N50-1</f>
@@ -14108,7 +14156,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>[Derived] klac/dist/20261025_科磊模型_v0.2.xlsx PL!E12…PL!G34</t>
+          <t>[Derived] klac/dist/20261025_科磊模型_v0.2.1.xlsx PL!E12…PL!G34</t>
         </is>
       </c>
       <c r="AH50">
@@ -14119,13 +14167,14 @@
         <f>IF(S50="未上市","未上市",IF(AND(AH50="不通過",OR(S50="強力買進",S50="買進",S50="未估值")),"收支不足",S50))</f>
         <v/>
       </c>
-      <c r="AJ50">
-        <f>IF(Q50&gt;0.5,"大於 50%",IF(Q50&gt;0.25,"25%–50%",IF(Q50&gt;=0,"0%–25%",IF(Q50&gt;=-0.25,"0%～−25%",IF(Q50&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ50" s="4" t="inlineStr">
+        <is>
+          <t>0%～−25%</t>
+        </is>
       </c>
       <c r="AK50" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 klac/dist/20261025_科磊模型_v0.2.xlsx Val!B132；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 klac/dist/20261025_科磊模型_v0.2.1.xlsx Val!B132；投資建議 klac/dist/20261025_科磊模型_v0.2.1.xlsx Val!B140；級距 klac/dist/20261025_科磊模型_v0.2.1.xlsx Val!B139</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14208,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>hanmi/dist/20261025_韓美半導體模型_v0.2.1.xlsx Val!B111</t>
+          <t>hanmi/dist/20261025_韓美半導體模型_v0.2.2.xlsx Val!B111</t>
         </is>
       </c>
       <c r="J51" s="4" t="n">
@@ -14167,7 +14216,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>hanmi/dist/20261025_韓美半導體模型_v0.2.1.xlsx Val!D96</t>
+          <t>hanmi/dist/20261025_韓美半導體模型_v0.2.2.xlsx Val!D96</t>
         </is>
       </c>
       <c r="N51">
@@ -14189,9 +14238,10 @@
         <f>P51/N51-1</f>
         <v/>
       </c>
-      <c r="S51">
-        <f>IF(Q51&gt;0.5,"強力買進",IF(Q51&gt;0.25,"買進",IF(Q51&gt;=-0.25,"中立",IF(Q51&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S51" s="4" t="inlineStr">
+        <is>
+          <t>強力放空</t>
+        </is>
       </c>
       <c r="T51">
         <f>64078.0210298826/N51-1</f>
@@ -14243,7 +14293,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>[Derived] hanmi/dist/20261025_韓美半導體模型_v0.2.1.xlsx PL!D11…PL!G31</t>
+          <t>[Derived] hanmi/dist/20261025_韓美半導體模型_v0.2.2.xlsx PL!D11…PL!G31</t>
         </is>
       </c>
       <c r="AH51">
@@ -14254,13 +14304,14 @@
         <f>IF(S51="未上市","未上市",IF(AND(AH51="不通過",OR(S51="強力買進",S51="買進",S51="未估值")),"收支不足",S51))</f>
         <v/>
       </c>
-      <c r="AJ51">
-        <f>IF(Q51&gt;0.5,"大於 50%",IF(Q51&gt;0.25,"25%–50%",IF(Q51&gt;=0,"0%–25%",IF(Q51&gt;=-0.25,"0%～−25%",IF(Q51&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ51" s="4" t="inlineStr">
+        <is>
+          <t>小於 −50%</t>
+        </is>
       </c>
       <c r="AK51" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 hanmi/dist/20261025_韓美半導體模型_v0.2.1.xlsx Val!B114；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 hanmi/dist/20261025_韓美半導體模型_v0.2.2.xlsx Val!B114；投資建議 hanmi/dist/20261025_韓美半導體模型_v0.2.2.xlsx Val!B123；級距 hanmi/dist/20261025_韓美半導體模型_v0.2.2.xlsx Val!B122</t>
         </is>
       </c>
     </row>
@@ -14294,7 +14345,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>ter/dist/20261025_泰瑞達模型_v0.1.xlsx Val!B126</t>
+          <t>ter/dist/20261025_泰瑞達模型_v0.1.1.xlsx Val!B126</t>
         </is>
       </c>
       <c r="J52" s="4" t="n">
@@ -14302,7 +14353,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>ter/dist/20261025_泰瑞達模型_v0.1.xlsx Val!D110</t>
+          <t>ter/dist/20261025_泰瑞達模型_v0.1.1.xlsx Val!D110</t>
         </is>
       </c>
       <c r="N52">
@@ -14324,9 +14375,10 @@
         <f>P52/N52-1</f>
         <v/>
       </c>
-      <c r="S52">
-        <f>IF(Q52&gt;0.5,"強力買進",IF(Q52&gt;0.25,"買進",IF(Q52&gt;=-0.25,"中立",IF(Q52&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S52" s="4" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
       </c>
       <c r="T52">
         <f>388.636638757835/N52-1</f>
@@ -14378,7 +14430,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>[Derived] ter/dist/20261025_泰瑞達模型_v0.1.xlsx PL!D12…PL!G34</t>
+          <t>[Derived] ter/dist/20261025_泰瑞達模型_v0.1.1.xlsx PL!D12…PL!G34</t>
         </is>
       </c>
       <c r="AH52">
@@ -14389,13 +14441,14 @@
         <f>IF(S52="未上市","未上市",IF(AND(AH52="不通過",OR(S52="強力買進",S52="買進",S52="未估值")),"收支不足",S52))</f>
         <v/>
       </c>
-      <c r="AJ52">
-        <f>IF(Q52&gt;0.5,"大於 50%",IF(Q52&gt;0.25,"25%–50%",IF(Q52&gt;=0,"0%–25%",IF(Q52&gt;=-0.25,"0%～−25%",IF(Q52&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ52" s="4" t="inlineStr">
+        <is>
+          <t>0%–25%</t>
+        </is>
       </c>
       <c r="AK52" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 ter/dist/20261025_泰瑞達模型_v0.1.xlsx Val!B129；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 ter/dist/20261025_泰瑞達模型_v0.1.1.xlsx Val!B129；投資建議 ter/dist/20261025_泰瑞達模型_v0.1.1.xlsx Val!B138；級距 ter/dist/20261025_泰瑞達模型_v0.1.1.xlsx Val!B137</t>
         </is>
       </c>
     </row>
@@ -14429,7 +14482,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>besi/dist/20261025_BESI模型_v0.1.xlsx Val!B112</t>
+          <t>besi/dist/20261025_BESI模型_v0.1.1.xlsx Val!B112</t>
         </is>
       </c>
       <c r="J53" s="4" t="n">
@@ -14437,7 +14490,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>besi/dist/20261025_BESI模型_v0.1.xlsx Val!D96</t>
+          <t>besi/dist/20261025_BESI模型_v0.1.1.xlsx Val!D96</t>
         </is>
       </c>
       <c r="N53">
@@ -14459,9 +14512,10 @@
         <f>P53/N53-1</f>
         <v/>
       </c>
-      <c r="S53">
-        <f>IF(Q53&gt;0.5,"強力買進",IF(Q53&gt;0.25,"買進",IF(Q53&gt;=-0.25,"中立",IF(Q53&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S53" s="4" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
       </c>
       <c r="T53">
         <f>188.684289175905/N53-1</f>
@@ -14513,7 +14567,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>[Derived] besi/dist/20261025_BESI模型_v0.1.xlsx PL!D11…PL!G31</t>
+          <t>[Derived] besi/dist/20261025_BESI模型_v0.1.1.xlsx PL!D11…PL!G31</t>
         </is>
       </c>
       <c r="AH53">
@@ -14524,13 +14578,14 @@
         <f>IF(S53="未上市","未上市",IF(AND(AH53="不通過",OR(S53="強力買進",S53="買進",S53="未估值")),"收支不足",S53))</f>
         <v/>
       </c>
-      <c r="AJ53">
-        <f>IF(Q53&gt;0.5,"大於 50%",IF(Q53&gt;0.25,"25%–50%",IF(Q53&gt;=0,"0%–25%",IF(Q53&gt;=-0.25,"0%～−25%",IF(Q53&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ53" s="4" t="inlineStr">
+        <is>
+          <t>0%～−25%</t>
+        </is>
       </c>
       <c r="AK53" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 besi/dist/20261025_BESI模型_v0.1.xlsx Val!B115；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 besi/dist/20261025_BESI模型_v0.1.1.xlsx Val!B115；投資建議 besi/dist/20261025_BESI模型_v0.1.1.xlsx Val!B124；級距 besi/dist/20261025_BESI模型_v0.1.1.xlsx Val!B123</t>
         </is>
       </c>
     </row>
@@ -14564,7 +14619,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>towa/dist/20261025_TOWA模型_v0.1.xlsx Val!B39</t>
+          <t>towa/dist/20261025_TOWA模型_v0.1.1.xlsx Val!B39</t>
         </is>
       </c>
       <c r="J54" s="4" t="n">
@@ -14572,7 +14627,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>towa/dist/20261025_TOWA模型_v0.1.xlsx Val!D23</t>
+          <t>towa/dist/20261025_TOWA模型_v0.1.1.xlsx Val!D23</t>
         </is>
       </c>
       <c r="N54">
@@ -14594,9 +14649,10 @@
         <f>P54/N54-1</f>
         <v/>
       </c>
-      <c r="S54">
-        <f>IF(Q54&gt;0.5,"強力買進",IF(Q54&gt;0.25,"買進",IF(Q54&gt;=-0.25,"中立",IF(Q54&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S54" s="4" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
       </c>
       <c r="T54">
         <f>1478.20786366597/N54-1</f>
@@ -14648,7 +14704,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>[Derived] towa/dist/20261025_TOWA模型_v0.1.xlsx PL!D14…PL!G42</t>
+          <t>[Derived] towa/dist/20261025_TOWA模型_v0.1.1.xlsx PL!D14…PL!G42</t>
         </is>
       </c>
       <c r="AH54">
@@ -14659,13 +14715,14 @@
         <f>IF(S54="未上市","未上市",IF(AND(AH54="不通過",OR(S54="強力買進",S54="買進",S54="未估值")),"收支不足",S54))</f>
         <v/>
       </c>
-      <c r="AJ54">
-        <f>IF(Q54&gt;0.5,"大於 50%",IF(Q54&gt;0.25,"25%–50%",IF(Q54&gt;=0,"0%–25%",IF(Q54&gt;=-0.25,"0%～−25%",IF(Q54&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ54" s="4" t="inlineStr">
+        <is>
+          <t>0%～−25%</t>
+        </is>
       </c>
       <c r="AK54" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 towa/dist/20261025_TOWA模型_v0.1.xlsx Val!B42；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 towa/dist/20261025_TOWA模型_v0.1.1.xlsx Val!B42；投資建議 towa/dist/20261025_TOWA模型_v0.1.1.xlsx Val!B125；級距 towa/dist/20261025_TOWA模型_v0.1.1.xlsx Val!B124</t>
         </is>
       </c>
     </row>
@@ -14699,7 +14756,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>accretech/dist/20261025_東京精密模型_v0.1.xlsx Val!B40</t>
+          <t>accretech/dist/20261025_東京精密模型_v0.1.1.xlsx Val!B40</t>
         </is>
       </c>
       <c r="J55" s="4" t="n">
@@ -14707,7 +14764,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>accretech/dist/20261025_東京精密模型_v0.1.xlsx Val!D23</t>
+          <t>accretech/dist/20261025_東京精密模型_v0.1.1.xlsx Val!D23</t>
         </is>
       </c>
       <c r="N55">
@@ -14729,9 +14786,10 @@
         <f>P55/N55-1</f>
         <v/>
       </c>
-      <c r="S55">
-        <f>IF(Q55&gt;0.5,"強力買進",IF(Q55&gt;0.25,"買進",IF(Q55&gt;=-0.25,"中立",IF(Q55&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S55" s="4" t="inlineStr">
+        <is>
+          <t>買進</t>
+        </is>
       </c>
       <c r="T55">
         <f>11632.8169386252/N55-1</f>
@@ -14783,7 +14841,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>[Derived] accretech/dist/20261025_東京精密模型_v0.1.xlsx PL!D12…PL!G34</t>
+          <t>[Derived] accretech/dist/20261025_東京精密模型_v0.1.1.xlsx PL!D12…PL!G34</t>
         </is>
       </c>
       <c r="AH55">
@@ -14794,13 +14852,14 @@
         <f>IF(S55="未上市","未上市",IF(AND(AH55="不通過",OR(S55="強力買進",S55="買進",S55="未估值")),"收支不足",S55))</f>
         <v/>
       </c>
-      <c r="AJ55">
-        <f>IF(Q55&gt;0.5,"大於 50%",IF(Q55&gt;0.25,"25%–50%",IF(Q55&gt;=0,"0%–25%",IF(Q55&gt;=-0.25,"0%～−25%",IF(Q55&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ55" s="4" t="inlineStr">
+        <is>
+          <t>25%–50%</t>
+        </is>
       </c>
       <c r="AK55" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 accretech/dist/20261025_東京精密模型_v0.1.xlsx Val!B43；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 accretech/dist/20261025_東京精密模型_v0.1.1.xlsx Val!B43；投資建議 accretech/dist/20261025_東京精密模型_v0.1.1.xlsx Val!B116；級距 accretech/dist/20261025_東京精密模型_v0.1.1.xlsx Val!B115</t>
         </is>
       </c>
     </row>
@@ -14834,7 +14893,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>foxconn/dist/20261025_鴻海模型_v0.2.xlsx Val!B120</t>
+          <t>foxconn/dist/20261025_鴻海模型_v0.2.1.xlsx Val!B120</t>
         </is>
       </c>
       <c r="J56" s="4" t="n">
@@ -14842,7 +14901,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>foxconn/dist/20261025_鴻海模型_v0.2.xlsx Val!D104</t>
+          <t>foxconn/dist/20261025_鴻海模型_v0.2.1.xlsx Val!D104</t>
         </is>
       </c>
       <c r="N56">
@@ -14864,9 +14923,10 @@
         <f>P56/N56-1</f>
         <v/>
       </c>
-      <c r="S56">
-        <f>IF(Q56&gt;0.5,"強力買進",IF(Q56&gt;0.25,"買進",IF(Q56&gt;=-0.25,"中立",IF(Q56&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S56" s="4" t="inlineStr">
+        <is>
+          <t>買進</t>
+        </is>
       </c>
       <c r="T56">
         <f>261.429965980011/N56-1</f>
@@ -14918,7 +14978,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>[Derived] foxconn/dist/20261025_鴻海模型_v0.2.xlsx PL!D13…PL!G39</t>
+          <t>[Derived] foxconn/dist/20261025_鴻海模型_v0.2.1.xlsx PL!D13…PL!G39</t>
         </is>
       </c>
       <c r="AH56">
@@ -14929,13 +14989,14 @@
         <f>IF(S56="未上市","未上市",IF(AND(AH56="不通過",OR(S56="強力買進",S56="買進",S56="未估值")),"收支不足",S56))</f>
         <v/>
       </c>
-      <c r="AJ56">
-        <f>IF(Q56&gt;0.5,"大於 50%",IF(Q56&gt;0.25,"25%–50%",IF(Q56&gt;=0,"0%–25%",IF(Q56&gt;=-0.25,"0%～−25%",IF(Q56&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ56" s="4" t="inlineStr">
+        <is>
+          <t>25%–50%</t>
+        </is>
       </c>
       <c r="AK56" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 foxconn/dist/20261025_鴻海模型_v0.2.xlsx Val!B123；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 foxconn/dist/20261025_鴻海模型_v0.2.1.xlsx Val!B123；投資建議 foxconn/dist/20261025_鴻海模型_v0.2.1.xlsx Val!B136；級距 foxconn/dist/20261025_鴻海模型_v0.2.1.xlsx Val!B135</t>
         </is>
       </c>
     </row>
@@ -14969,7 +15030,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>wistron/dist/20261025_緯創模型_v0.1.xlsx Val!B39</t>
+          <t>wistron/dist/20261025_緯創模型_v0.1.1.xlsx Val!B39</t>
         </is>
       </c>
       <c r="J57" s="4" t="n">
@@ -14977,7 +15038,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>wistron/dist/20261025_緯創模型_v0.1.xlsx Val!D23</t>
+          <t>wistron/dist/20261025_緯創模型_v0.1.1.xlsx Val!D23</t>
         </is>
       </c>
       <c r="N57">
@@ -14999,9 +15060,10 @@
         <f>P57/N57-1</f>
         <v/>
       </c>
-      <c r="S57">
-        <f>IF(Q57&gt;0.5,"強力買進",IF(Q57&gt;0.25,"買進",IF(Q57&gt;=-0.25,"中立",IF(Q57&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S57" s="4" t="inlineStr">
+        <is>
+          <t>強力買進</t>
+        </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -15044,7 +15106,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>[Derived] wistron/dist/20261025_緯創模型_v0.1.xlsx PL!D13…PL!J41</t>
+          <t>[Derived] wistron/dist/20261025_緯創模型_v0.1.1.xlsx PL!D13…PL!J41</t>
         </is>
       </c>
       <c r="AH57">
@@ -15055,13 +15117,14 @@
         <f>IF(S57="未上市","未上市",IF(AND(AH57="不通過",OR(S57="強力買進",S57="買進",S57="未估值")),"收支不足",S57))</f>
         <v/>
       </c>
-      <c r="AJ57">
-        <f>IF(Q57&gt;0.5,"大於 50%",IF(Q57&gt;0.25,"25%–50%",IF(Q57&gt;=0,"0%–25%",IF(Q57&gt;=-0.25,"0%～−25%",IF(Q57&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ57" s="4" t="inlineStr">
+        <is>
+          <t>大於 50%</t>
+        </is>
       </c>
       <c r="AK57" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 wistron/dist/20261025_緯創模型_v0.1.xlsx Val!B42；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 wistron/dist/20261025_緯創模型_v0.1.1.xlsx Val!B42；投資建議 wistron/dist/20261025_緯創模型_v0.1.1.xlsx Val!B136；級距 wistron/dist/20261025_緯創模型_v0.1.1.xlsx Val!B135</t>
         </is>
       </c>
     </row>
@@ -15095,7 +15158,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>wiwynn/dist/20261025_緯穎模型_v0.1.xlsx Val!B39</t>
+          <t>wiwynn/dist/20261025_緯穎模型_v0.1.1.xlsx Val!B39</t>
         </is>
       </c>
       <c r="J58" s="4" t="n">
@@ -15103,7 +15166,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>wiwynn/dist/20261025_緯穎模型_v0.1.xlsx Val!D23</t>
+          <t>wiwynn/dist/20261025_緯穎模型_v0.1.1.xlsx Val!D23</t>
         </is>
       </c>
       <c r="N58">
@@ -15125,9 +15188,10 @@
         <f>P58/N58-1</f>
         <v/>
       </c>
-      <c r="S58">
-        <f>IF(Q58&gt;0.5,"強力買進",IF(Q58&gt;0.25,"買進",IF(Q58&gt;=-0.25,"中立",IF(Q58&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S58" s="4" t="inlineStr">
+        <is>
+          <t>強力買進</t>
+        </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -15170,7 +15234,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>[Derived] wiwynn/dist/20261025_緯穎模型_v0.1.xlsx PL!D12…PL!J38</t>
+          <t>[Derived] wiwynn/dist/20261025_緯穎模型_v0.1.1.xlsx PL!D12…PL!J38</t>
         </is>
       </c>
       <c r="AH58">
@@ -15181,13 +15245,14 @@
         <f>IF(S58="未上市","未上市",IF(AND(AH58="不通過",OR(S58="強力買進",S58="買進",S58="未估值")),"收支不足",S58))</f>
         <v/>
       </c>
-      <c r="AJ58">
-        <f>IF(Q58&gt;0.5,"大於 50%",IF(Q58&gt;0.25,"25%–50%",IF(Q58&gt;=0,"0%–25%",IF(Q58&gt;=-0.25,"0%～−25%",IF(Q58&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ58" s="4" t="inlineStr">
+        <is>
+          <t>大於 50%</t>
+        </is>
       </c>
       <c r="AK58" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 wiwynn/dist/20261025_緯穎模型_v0.1.xlsx Val!B42；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 wiwynn/dist/20261025_緯穎模型_v0.1.1.xlsx Val!B42；投資建議 wiwynn/dist/20261025_緯穎模型_v0.1.1.xlsx Val!B136；級距 wiwynn/dist/20261025_緯穎模型_v0.1.1.xlsx Val!B135</t>
         </is>
       </c>
     </row>
@@ -15349,7 +15414,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>smci/dist/20261025_美超微模型_v0.1.xlsx Val!B39</t>
+          <t>smci/dist/20261025_美超微模型_v0.1.1.xlsx Val!B39</t>
         </is>
       </c>
       <c r="J60" s="4" t="n">
@@ -15357,7 +15422,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>smci/dist/20261025_美超微模型_v0.1.xlsx Val!D23</t>
+          <t>smci/dist/20261025_美超微模型_v0.1.1.xlsx Val!D23</t>
         </is>
       </c>
       <c r="N60">
@@ -15379,9 +15444,10 @@
         <f>P60/N60-1</f>
         <v/>
       </c>
-      <c r="S60">
-        <f>IF(Q60&gt;0.5,"強力買進",IF(Q60&gt;0.25,"買進",IF(Q60&gt;=-0.25,"中立",IF(Q60&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S60" s="4" t="inlineStr">
+        <is>
+          <t>強力買進</t>
+        </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
@@ -15424,7 +15490,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>[Derived] smci/dist/20261025_美超微模型_v0.1.xlsx PL!E12…PL!J38</t>
+          <t>[Derived] smci/dist/20261025_美超微模型_v0.1.1.xlsx PL!E12…PL!J38</t>
         </is>
       </c>
       <c r="AH60">
@@ -15435,13 +15501,14 @@
         <f>IF(S60="未上市","未上市",IF(AND(AH60="不通過",OR(S60="強力買進",S60="買進",S60="未估值")),"收支不足",S60))</f>
         <v/>
       </c>
-      <c r="AJ60">
-        <f>IF(Q60&gt;0.5,"大於 50%",IF(Q60&gt;0.25,"25%–50%",IF(Q60&gt;=0,"0%–25%",IF(Q60&gt;=-0.25,"0%～−25%",IF(Q60&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ60" s="4" t="inlineStr">
+        <is>
+          <t>大於 50%</t>
+        </is>
       </c>
       <c r="AK60" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 smci/dist/20261025_美超微模型_v0.1.xlsx Val!B42；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 smci/dist/20261025_美超微模型_v0.1.1.xlsx Val!B42；投資建議 smci/dist/20261025_美超微模型_v0.1.1.xlsx Val!B136；級距 smci/dist/20261025_美超微模型_v0.1.1.xlsx Val!B135</t>
         </is>
       </c>
     </row>
@@ -15471,19 +15538,19 @@
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>3955.89398288466</v>
+        <v>3965.52216912282</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>avc/dist/20261025_奇鋐模型_v0.2.xlsx Val!B119</t>
+          <t>avc/dist/20261025_奇鋐模型_v0.2.1.xlsx Val!B119</t>
         </is>
       </c>
       <c r="J61" s="4" t="n">
-        <v>2016.1990416386</v>
+        <v>1834.66717881608</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>avc/dist/20261025_奇鋐模型_v0.2.xlsx Val!D104</t>
+          <t>avc/dist/20261025_奇鋐模型_v0.2.1.xlsx Val!D104</t>
         </is>
       </c>
       <c r="N61">
@@ -15499,18 +15566,19 @@
         <v/>
       </c>
       <c r="Q61" s="4" t="n">
-        <v>0.257835924605614</v>
+        <v>0.26089735107244</v>
       </c>
       <c r="R61">
         <f>P61/N61-1</f>
         <v/>
       </c>
-      <c r="S61">
-        <f>IF(Q61&gt;0.5,"強力買進",IF(Q61&gt;0.25,"買進",IF(Q61&gt;=-0.25,"中立",IF(Q61&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S61" s="4" t="inlineStr">
+        <is>
+          <t>買進</t>
+        </is>
       </c>
       <c r="T61">
-        <f>2025.40760731771/N61-1</f>
+        <f>2031.07059401483/N61-1</f>
         <v/>
       </c>
       <c r="U61" t="inlineStr">
@@ -15520,12 +15588,12 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>15.0 ／ 17.7 ／ 21.9</t>
+          <t>14.0 ／ 17.7 ／ 24.1</t>
         </is>
       </c>
       <c r="W61" s="1" t="inlineStr">
         <is>
-          <t>DCF 目標價 3,027.2（Val!B105）；Comparable 目標價 4,884.6（Val!B120）；市場共識目標價 4,130.0（Val!B121，外部、僅供對照）；價格帶 C～A 情境 DCF 2,016.2～3,706.7</t>
+          <t>DCF 目標價 3,002.5（Val!B105）；Comparable 目標價 4,928.5（Val!B120）；市場共識目標價 4,130.0（Val!B121，外部、僅供對照）；價格帶 C～A 情境 DCF 1,834.7～3,745.5</t>
         </is>
       </c>
       <c r="Z61">
@@ -15548,18 +15616,18 @@
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>8 個情境年度淨利（不含實績），全部為正</t>
+          <t>10 個情境年度淨利（不含實績），全部為正</t>
         </is>
       </c>
       <c r="AE61" s="4" t="n">
-        <v>547.0033990860203</v>
+        <v>671.2521938360467</v>
       </c>
       <c r="AF61" s="4" t="n">
         <v>41.5923093275</v>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>[Derived] avc/dist/20261025_奇鋐模型_v0.2.xlsx PL!D14…PL!G42</t>
+          <t>[Derived] avc/dist/20261025_奇鋐模型_v0.2.1.xlsx PL!D14…PL!G42</t>
         </is>
       </c>
       <c r="AH61">
@@ -15570,13 +15638,14 @@
         <f>IF(S61="未上市","未上市",IF(AND(AH61="不通過",OR(S61="強力買進",S61="買進",S61="未估值")),"收支不足",S61))</f>
         <v/>
       </c>
-      <c r="AJ61">
-        <f>IF(Q61&gt;0.5,"大於 50%",IF(Q61&gt;0.25,"25%–50%",IF(Q61&gt;=0,"0%–25%",IF(Q61&gt;=-0.25,"0%～−25%",IF(Q61&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ61" s="4" t="inlineStr">
+        <is>
+          <t>25%–50%</t>
+        </is>
       </c>
       <c r="AK61" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 avc/dist/20261025_奇鋐模型_v0.2.xlsx Val!B122；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 avc/dist/20261025_奇鋐模型_v0.2.1.xlsx Val!B122；投資建議 avc/dist/20261025_奇鋐模型_v0.2.1.xlsx Val!B135；級距 avc/dist/20261025_奇鋐模型_v0.2.1.xlsx Val!B134</t>
         </is>
       </c>
     </row>
@@ -15610,7 +15679,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>liteon/dist/20261025_光寶模型_v0.1.xlsx Val!B40</t>
+          <t>liteon/dist/20261025_光寶模型_v0.1.1.xlsx Val!B40</t>
         </is>
       </c>
       <c r="J62" s="4" t="n">
@@ -15618,7 +15687,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>liteon/dist/20261025_光寶模型_v0.1.xlsx Val!D23</t>
+          <t>liteon/dist/20261025_光寶模型_v0.1.1.xlsx Val!D23</t>
         </is>
       </c>
       <c r="N62">
@@ -15640,9 +15709,10 @@
         <f>P62/N62-1</f>
         <v/>
       </c>
-      <c r="S62">
-        <f>IF(Q62&gt;0.5,"強力買進",IF(Q62&gt;0.25,"買進",IF(Q62&gt;=-0.25,"中立",IF(Q62&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S62" s="4" t="inlineStr">
+        <is>
+          <t>強力買進</t>
+        </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
@@ -15685,7 +15755,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>[Derived] liteon/dist/20261025_光寶模型_v0.1.xlsx PL!D12…PL!J38</t>
+          <t>[Derived] liteon/dist/20261025_光寶模型_v0.1.1.xlsx PL!D12…PL!J38</t>
         </is>
       </c>
       <c r="AH62">
@@ -15696,13 +15766,14 @@
         <f>IF(S62="未上市","未上市",IF(AND(AH62="不通過",OR(S62="強力買進",S62="買進",S62="未估值")),"收支不足",S62))</f>
         <v/>
       </c>
-      <c r="AJ62">
-        <f>IF(Q62&gt;0.5,"大於 50%",IF(Q62&gt;0.25,"25%–50%",IF(Q62&gt;=0,"0%–25%",IF(Q62&gt;=-0.25,"0%～−25%",IF(Q62&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ62" s="4" t="inlineStr">
+        <is>
+          <t>大於 50%</t>
+        </is>
       </c>
       <c r="AK62" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 liteon/dist/20261025_光寶模型_v0.1.xlsx Val!B43；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 liteon/dist/20261025_光寶模型_v0.1.1.xlsx Val!B43；投資建議 liteon/dist/20261025_光寶模型_v0.1.1.xlsx Val!B119；級距 liteon/dist/20261025_光寶模型_v0.1.1.xlsx Val!B118</t>
         </is>
       </c>
     </row>
@@ -15736,7 +15807,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>auras/dist/20261025_雙鴻模型_v0.1.xlsx Val!B39</t>
+          <t>auras/dist/20261025_雙鴻模型_v0.1.1.xlsx Val!B39</t>
         </is>
       </c>
       <c r="J63" s="4" t="n">
@@ -15744,7 +15815,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>auras/dist/20261025_雙鴻模型_v0.1.xlsx Val!D23</t>
+          <t>auras/dist/20261025_雙鴻模型_v0.1.1.xlsx Val!D23</t>
         </is>
       </c>
       <c r="N63">
@@ -15766,9 +15837,10 @@
         <f>P63/N63-1</f>
         <v/>
       </c>
-      <c r="S63">
-        <f>IF(Q63&gt;0.5,"強力買進",IF(Q63&gt;0.25,"買進",IF(Q63&gt;=-0.25,"中立",IF(Q63&gt;=-0.5,"放空","強力放空"))))</f>
-        <v/>
+      <c r="S63" s="4" t="inlineStr">
+        <is>
+          <t>強力買進</t>
+        </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -15811,7 +15883,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>[Derived] auras/dist/20261025_雙鴻模型_v0.1.xlsx PL!D14…PL!G42</t>
+          <t>[Derived] auras/dist/20261025_雙鴻模型_v0.1.1.xlsx PL!D14…PL!G42</t>
         </is>
       </c>
       <c r="AH63">
@@ -15822,13 +15894,14 @@
         <f>IF(S63="未上市","未上市",IF(AND(AH63="不通過",OR(S63="強力買進",S63="買進",S63="未估值")),"收支不足",S63))</f>
         <v/>
       </c>
-      <c r="AJ63">
-        <f>IF(Q63&gt;0.5,"大於 50%",IF(Q63&gt;0.25,"25%–50%",IF(Q63&gt;=0,"0%–25%",IF(Q63&gt;=-0.25,"0%～−25%",IF(Q63&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v/>
+      <c r="AJ63" s="4" t="inlineStr">
+        <is>
+          <t>大於 50%</t>
+        </is>
       </c>
       <c r="AK63" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 auras/dist/20261025_雙鴻模型_v0.1.xlsx Val!B42；投資建議：模型尚未補列，依 AI半導體 固定規則自算；級距：模型尚未補列，依 AI半導體 固定規則自算</t>
+          <t>上檔空間 auras/dist/20261025_雙鴻模型_v0.1.1.xlsx Val!B42；投資建議 auras/dist/20261025_雙鴻模型_v0.1.1.xlsx Val!B130；級距 auras/dist/20261025_雙鴻模型_v0.1.1.xlsx Val!B129</t>
         </is>
       </c>
     </row>
@@ -15858,19 +15931,19 @@
         </is>
       </c>
       <c r="F64" s="4" t="n">
-        <v>3889.06729451463</v>
+        <v>3902.82839585769</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>jentech/dist/20261025_健策模型_v0.1.xlsx Val!B40</t>
+          <t>jentech/dist/20261025_健策模型_v0.1.1.xlsx Val!B40</t>
         </is>
       </c>
       <c r="J64" s="4" t="n">
-        <v>1371.95946165303</v>
+        <v>1351.67225447468</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>jentech/dist/20261025_健策模型_v0.1.xlsx Val!D23</t>
+          <t>jentech/dist/20261025_健策模型_v0.1.1.xlsx Val!D23</t>
         </is>
       </c>
       <c r="N64">
@@ -15886,7 +15959,7 @@
         <v/>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>-0.359296986076668</v>
+        <v>-0.3570299183101</v>
       </c>
       <c r="R64">
         <f>P64/N64-1</f>
@@ -15899,12 +15972,12 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>23.7 ／ 36.4 ／ 59.8</t>
+          <t>23.4 ／ 36.4 ／ 60.3</t>
         </is>
       </c>
       <c r="W64" s="1" t="inlineStr">
         <is>
-          <t>DCF 目標價 3,242.1（Val!B24）；Comparable 目標價 4,536.0（Val!B41）；市場共識目標價 7,204.0（Val!B42，外部、僅供對照）；價格帶 C～A 情境 DCF 1,372.0～5,003.3</t>
+          <t>DCF 目標價 3,247.2（Val!B24）；Comparable 目標價 4,558.5（Val!B41）；市場共識目標價 7,204.0（Val!B42，外部、僅供對照）；價格帶 C～A 情境 DCF 1,351.7～5,032.8</t>
         </is>
       </c>
       <c r="Z64">
@@ -15931,14 +16004,14 @@
         </is>
       </c>
       <c r="AE64" s="4" t="n">
-        <v>568.2809424571311</v>
+        <v>569.3703689419929</v>
       </c>
       <c r="AF64" s="4" t="n">
         <v>10.3442061825</v>
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>[Derived] jentech/dist/20261025_健策模型_v0.1.xlsx PL!D13…PL!J41</t>
+          <t>[Derived] jentech/dist/20261025_健策模型_v0.1.1.xlsx PL!D13…PL!J41</t>
         </is>
       </c>
       <c r="AH64">
@@ -15956,7 +16029,7 @@
       </c>
       <c r="AK64" s="1" t="inlineStr">
         <is>
-          <t>上檔空間 jentech/dist/20261025_健策模型_v0.1.xlsx Val!B43；投資建議 jentech/dist/20261025_健策模型_v0.1.xlsx Val!B46；級距 jentech/dist/20261025_健策模型_v0.1.xlsx Val!B45</t>
+          <t>上檔空間 jentech/dist/20261025_健策模型_v0.1.1.xlsx Val!B43；投資建議 jentech/dist/20261025_健策模型_v0.1.1.xlsx Val!B46；級距 jentech/dist/20261025_健策模型_v0.1.1.xlsx Val!B45</t>
         </is>
       </c>
     </row>
